--- a/research/traditional_assets/database/data/hungary/hungary_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_business_consumer_services.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1113280538548104</v>
+        <v>0.111268808606341</v>
       </c>
       <c r="C2">
-        <v>2.611756106718142</v>
+        <v>2.58611191696804</v>
       </c>
       <c r="D2">
-        <v>1.381756106718142</v>
+        <v>1.382171916968041</v>
       </c>
       <c r="E2">
-        <v>-0.136</v>
+        <v>-0.10994</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02606</v>
       </c>
       <c r="G2">
         <v>1.23</v>
@@ -1433,28 +1433,28 @@
         <v>0.349</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001310818</v>
       </c>
       <c r="N2">
-        <v>0.349</v>
+        <v>0.347689182</v>
       </c>
       <c r="O2">
-        <v>0.03140999999999999</v>
+        <v>0.03129202638</v>
       </c>
       <c r="P2">
-        <v>0.31759</v>
+        <v>0.31639715562</v>
       </c>
       <c r="Q2">
-        <v>0.35159</v>
+        <v>0.35039715562</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1113280538548104</v>
+        <v>0.1119303824306475</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927494</v>
+        <v>0.9622776417862282</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>266.2459624448245</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.111268808606341</v>
+        <v>0.1112095633578717</v>
       </c>
       <c r="C3">
-        <v>2.58611191696804</v>
+        <v>2.560467977551857</v>
       </c>
       <c r="D3">
-        <v>1.382171916968041</v>
+        <v>1.382587977551857</v>
       </c>
       <c r="E3">
-        <v>-0.10994</v>
+        <v>-0.08388000000000001</v>
       </c>
       <c r="F3">
-        <v>0.02606</v>
+        <v>0.05212000000000001</v>
       </c>
       <c r="G3">
         <v>1.23</v>
@@ -1515,28 +1515,28 @@
         <v>0.349</v>
       </c>
       <c r="M3">
-        <v>0.001310818</v>
+        <v>0.002621636</v>
       </c>
       <c r="N3">
-        <v>0.347689182</v>
+        <v>0.346378364</v>
       </c>
       <c r="O3">
-        <v>0.03129202638</v>
+        <v>0.03117405276</v>
       </c>
       <c r="P3">
-        <v>0.31639715562</v>
+        <v>0.31520431124</v>
       </c>
       <c r="Q3">
-        <v>0.35039715562</v>
+        <v>0.34920431124</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1119303824306475</v>
+        <v>0.1125450034263997</v>
       </c>
       <c r="T3">
-        <v>0.9622776417862282</v>
+        <v>0.9712211261673291</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>266.2459624448245</v>
+        <v>133.1229812224122</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1112095633578717</v>
+        <v>0.1111503181094024</v>
       </c>
       <c r="C4">
-        <v>2.560467977551857</v>
+        <v>2.534824288695725</v>
       </c>
       <c r="D4">
-        <v>1.382587977551857</v>
+        <v>1.383004288695725</v>
       </c>
       <c r="E4">
-        <v>-0.08388000000000001</v>
+        <v>-0.05782</v>
       </c>
       <c r="F4">
-        <v>0.05212000000000001</v>
+        <v>0.07818000000000001</v>
       </c>
       <c r="G4">
         <v>1.23</v>
@@ -1597,28 +1597,28 @@
         <v>0.349</v>
       </c>
       <c r="M4">
-        <v>0.002621636</v>
+        <v>0.003932454</v>
       </c>
       <c r="N4">
-        <v>0.346378364</v>
+        <v>0.345067546</v>
       </c>
       <c r="O4">
-        <v>0.03117405276</v>
+        <v>0.03105607914</v>
       </c>
       <c r="P4">
-        <v>0.31520431124</v>
+        <v>0.31401146686</v>
       </c>
       <c r="Q4">
-        <v>0.34920431124</v>
+        <v>0.3480114668600001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1125450034263997</v>
+        <v>0.1131722970200025</v>
       </c>
       <c r="T4">
-        <v>0.9712211261673291</v>
+        <v>0.9803490122882464</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>133.1229812224122</v>
+        <v>88.74865414827484</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1111503181094024</v>
+        <v>0.1110910728609331</v>
       </c>
       <c r="C5">
-        <v>2.534824288695725</v>
+        <v>2.509180850626052</v>
       </c>
       <c r="D5">
-        <v>1.383004288695725</v>
+        <v>1.383420850626052</v>
       </c>
       <c r="E5">
-        <v>-0.05782</v>
+        <v>-0.03176</v>
       </c>
       <c r="F5">
-        <v>0.07818000000000001</v>
+        <v>0.10424</v>
       </c>
       <c r="G5">
         <v>1.23</v>
@@ -1679,28 +1679,28 @@
         <v>0.349</v>
       </c>
       <c r="M5">
-        <v>0.003932454</v>
+        <v>0.005243272</v>
       </c>
       <c r="N5">
-        <v>0.345067546</v>
+        <v>0.343756728</v>
       </c>
       <c r="O5">
-        <v>0.03105607914</v>
+        <v>0.03093810551999999</v>
       </c>
       <c r="P5">
-        <v>0.31401146686</v>
+        <v>0.31281862248</v>
       </c>
       <c r="Q5">
-        <v>0.3480114668600001</v>
+        <v>0.34681862248</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1131722970200025</v>
+        <v>0.1138126592301386</v>
       </c>
       <c r="T5">
-        <v>0.9803490122882464</v>
+        <v>0.9896670627033495</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.74865414827484</v>
+        <v>66.56149061120612</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1110910728609331</v>
+        <v>0.1110318276124637</v>
       </c>
       <c r="C6">
-        <v>2.509180850626052</v>
+        <v>2.483537663569516</v>
       </c>
       <c r="D6">
-        <v>1.383420850626052</v>
+        <v>1.383837663569516</v>
       </c>
       <c r="E6">
-        <v>-0.03176</v>
+        <v>-0.005699999999999983</v>
       </c>
       <c r="F6">
-        <v>0.10424</v>
+        <v>0.1303</v>
       </c>
       <c r="G6">
         <v>1.23</v>
@@ -1761,28 +1761,28 @@
         <v>0.349</v>
       </c>
       <c r="M6">
-        <v>0.005243272</v>
+        <v>0.006554090000000001</v>
       </c>
       <c r="N6">
-        <v>0.343756728</v>
+        <v>0.34244591</v>
       </c>
       <c r="O6">
-        <v>0.03093810551999999</v>
+        <v>0.0308201319</v>
       </c>
       <c r="P6">
-        <v>0.31281862248</v>
+        <v>0.3116257781</v>
       </c>
       <c r="Q6">
-        <v>0.34681862248</v>
+        <v>0.3456257781</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1138126592301386</v>
+        <v>0.1144665027499618</v>
       </c>
       <c r="T6">
-        <v>0.9896670627033495</v>
+        <v>0.9991812826008758</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.56149061120612</v>
+        <v>53.24919248896489</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1110318276124637</v>
+        <v>0.1109725823639944</v>
       </c>
       <c r="C7">
-        <v>2.483537663569516</v>
+        <v>2.457894727753071</v>
       </c>
       <c r="D7">
-        <v>1.383837663569516</v>
+        <v>1.384254727753071</v>
       </c>
       <c r="E7">
-        <v>-0.005699999999999983</v>
+        <v>0.02036000000000002</v>
       </c>
       <c r="F7">
-        <v>0.1303</v>
+        <v>0.15636</v>
       </c>
       <c r="G7">
         <v>1.23</v>
@@ -1843,28 +1843,28 @@
         <v>0.349</v>
       </c>
       <c r="M7">
-        <v>0.006554090000000001</v>
+        <v>0.007864908</v>
       </c>
       <c r="N7">
-        <v>0.34244591</v>
+        <v>0.341135092</v>
       </c>
       <c r="O7">
-        <v>0.0308201319</v>
+        <v>0.03070215828</v>
       </c>
       <c r="P7">
-        <v>0.3116257781</v>
+        <v>0.31043293372</v>
       </c>
       <c r="Q7">
-        <v>0.3456257781</v>
+        <v>0.34443293372</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1144665027499618</v>
+        <v>0.1151342578340366</v>
       </c>
       <c r="T7">
-        <v>0.9991812826008758</v>
+        <v>1.008897932708988</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.24919248896489</v>
+        <v>44.37432707413742</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1109725823639944</v>
+        <v>0.1109133371155251</v>
       </c>
       <c r="C8">
-        <v>2.457894727753071</v>
+        <v>2.432252043403942</v>
       </c>
       <c r="D8">
-        <v>1.384254727753071</v>
+        <v>1.384672043403943</v>
       </c>
       <c r="E8">
-        <v>0.02036000000000002</v>
+        <v>0.04641999999999999</v>
       </c>
       <c r="F8">
-        <v>0.15636</v>
+        <v>0.18242</v>
       </c>
       <c r="G8">
         <v>1.23</v>
@@ -1925,28 +1925,28 @@
         <v>0.349</v>
       </c>
       <c r="M8">
-        <v>0.007864908</v>
+        <v>0.009175725999999999</v>
       </c>
       <c r="N8">
-        <v>0.341135092</v>
+        <v>0.339824274</v>
       </c>
       <c r="O8">
-        <v>0.03070215828</v>
+        <v>0.03058418466</v>
       </c>
       <c r="P8">
-        <v>0.31043293372</v>
+        <v>0.30924008934</v>
       </c>
       <c r="Q8">
-        <v>0.34443293372</v>
+        <v>0.34324008934</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1151342578340366</v>
+        <v>0.1158163732425001</v>
       </c>
       <c r="T8">
-        <v>1.008897932708988</v>
+        <v>1.018823543034479</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.37432707413742</v>
+        <v>38.03513749211779</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1109133371155251</v>
+        <v>0.1108540918670557</v>
       </c>
       <c r="C9">
-        <v>2.432252043403942</v>
+        <v>2.406609610749632</v>
       </c>
       <c r="D9">
-        <v>1.384672043403943</v>
+        <v>1.385089610749632</v>
       </c>
       <c r="E9">
-        <v>0.04642000000000002</v>
+        <v>0.07248000000000002</v>
       </c>
       <c r="F9">
-        <v>0.18242</v>
+        <v>0.20848</v>
       </c>
       <c r="G9">
         <v>1.23</v>
@@ -2007,28 +2007,28 @@
         <v>0.349</v>
       </c>
       <c r="M9">
-        <v>0.009175726</v>
+        <v>0.010486544</v>
       </c>
       <c r="N9">
-        <v>0.339824274</v>
+        <v>0.338513456</v>
       </c>
       <c r="O9">
-        <v>0.03058418466</v>
+        <v>0.03046621104</v>
       </c>
       <c r="P9">
-        <v>0.30924008934</v>
+        <v>0.30804724496</v>
       </c>
       <c r="Q9">
-        <v>0.34324008934</v>
+        <v>0.3420472449600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1158163732425001</v>
+        <v>0.1165133172467997</v>
       </c>
       <c r="T9">
-        <v>1.018823543034479</v>
+        <v>1.02896492749748</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.03513749211778</v>
+        <v>33.28074530560306</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1108540918670557</v>
+        <v>0.1107948466185864</v>
       </c>
       <c r="C10">
-        <v>2.406609610749632</v>
+        <v>2.380967430017914</v>
       </c>
       <c r="D10">
-        <v>1.385089610749632</v>
+        <v>1.385507430017914</v>
       </c>
       <c r="E10">
-        <v>0.07248000000000002</v>
+        <v>0.09854000000000002</v>
       </c>
       <c r="F10">
-        <v>0.20848</v>
+        <v>0.23454</v>
       </c>
       <c r="G10">
         <v>1.23</v>
@@ -2089,28 +2089,28 @@
         <v>0.349</v>
       </c>
       <c r="M10">
-        <v>0.010486544</v>
+        <v>0.011797362</v>
       </c>
       <c r="N10">
-        <v>0.338513456</v>
+        <v>0.337202638</v>
       </c>
       <c r="O10">
-        <v>0.03046621104</v>
+        <v>0.03034823742</v>
       </c>
       <c r="P10">
-        <v>0.30804724496</v>
+        <v>0.30685440058</v>
       </c>
       <c r="Q10">
-        <v>0.3420472449600001</v>
+        <v>0.34085440058</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1165133172467997</v>
+        <v>0.1172255787017433</v>
       </c>
       <c r="T10">
-        <v>1.02896492749748</v>
+        <v>1.039329199531097</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.28074530560306</v>
+        <v>29.58288471609161</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1107948466185864</v>
+        <v>0.1107356013701171</v>
       </c>
       <c r="C11">
-        <v>2.380967430017914</v>
+        <v>2.355325501436838</v>
       </c>
       <c r="D11">
-        <v>1.385507430017914</v>
+        <v>1.385925501436838</v>
       </c>
       <c r="E11">
-        <v>0.09854000000000002</v>
+        <v>0.1246</v>
       </c>
       <c r="F11">
-        <v>0.23454</v>
+        <v>0.2606</v>
       </c>
       <c r="G11">
         <v>1.23</v>
@@ -2171,28 +2171,28 @@
         <v>0.349</v>
       </c>
       <c r="M11">
-        <v>0.011797362</v>
+        <v>0.01310818</v>
       </c>
       <c r="N11">
-        <v>0.337202638</v>
+        <v>0.33589182</v>
       </c>
       <c r="O11">
-        <v>0.03034823742</v>
+        <v>0.03023026379999999</v>
       </c>
       <c r="P11">
-        <v>0.30685440058</v>
+        <v>0.3056615562</v>
       </c>
       <c r="Q11">
-        <v>0.34085440058</v>
+        <v>0.3396615562</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1172255787017433</v>
+        <v>0.117953668189019</v>
       </c>
       <c r="T11">
-        <v>1.039329199531097</v>
+        <v>1.049923788721016</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.58288471609161</v>
+        <v>26.62459624448245</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1107356013701171</v>
+        <v>0.1106763561216478</v>
       </c>
       <c r="C12">
-        <v>2.355325501436838</v>
+        <v>2.329683825234731</v>
       </c>
       <c r="D12">
-        <v>1.385925501436838</v>
+        <v>1.386343825234731</v>
       </c>
       <c r="E12">
-        <v>0.1246</v>
+        <v>0.15066</v>
       </c>
       <c r="F12">
-        <v>0.2606000000000001</v>
+        <v>0.28666</v>
       </c>
       <c r="G12">
         <v>1.23</v>
@@ -2253,28 +2253,28 @@
         <v>0.349</v>
       </c>
       <c r="M12">
-        <v>0.01310818</v>
+        <v>0.014418998</v>
       </c>
       <c r="N12">
-        <v>0.33589182</v>
+        <v>0.334581002</v>
       </c>
       <c r="O12">
-        <v>0.03023026379999999</v>
+        <v>0.03011229017999999</v>
       </c>
       <c r="P12">
-        <v>0.3056615562</v>
+        <v>0.30446871182</v>
       </c>
       <c r="Q12">
-        <v>0.3396615562</v>
+        <v>0.33846871182</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.117953668189019</v>
+        <v>0.1186981192378065</v>
       </c>
       <c r="T12">
-        <v>1.049923788721016</v>
+        <v>1.060756458566889</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.62459624448244</v>
+        <v>24.20417840407495</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1106763561216478</v>
+        <v>0.1106171108731784</v>
       </c>
       <c r="C13">
-        <v>2.329683825234731</v>
+        <v>2.304042401640192</v>
       </c>
       <c r="D13">
-        <v>1.386343825234731</v>
+        <v>1.386762401640192</v>
       </c>
       <c r="E13">
-        <v>0.15066</v>
+        <v>0.17672</v>
       </c>
       <c r="F13">
-        <v>0.28666</v>
+        <v>0.3127200000000001</v>
       </c>
       <c r="G13">
         <v>1.23</v>
@@ -2335,28 +2335,28 @@
         <v>0.349</v>
       </c>
       <c r="M13">
-        <v>0.014418998</v>
+        <v>0.015729816</v>
       </c>
       <c r="N13">
-        <v>0.334581002</v>
+        <v>0.333270184</v>
       </c>
       <c r="O13">
-        <v>0.03011229017999999</v>
+        <v>0.02999431656</v>
       </c>
       <c r="P13">
-        <v>0.30446871182</v>
+        <v>0.30327586744</v>
       </c>
       <c r="Q13">
-        <v>0.33846871182</v>
+        <v>0.33727586744</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1186981192378065</v>
+        <v>0.1194594896286118</v>
       </c>
       <c r="T13">
-        <v>1.060756458566889</v>
+        <v>1.071835325454713</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.20417840407495</v>
+        <v>22.18716353706871</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1106171108731784</v>
+        <v>0.1105578656247091</v>
       </c>
       <c r="C14">
-        <v>2.304042401640192</v>
+        <v>2.278401230882099</v>
       </c>
       <c r="D14">
-        <v>1.386762401640192</v>
+        <v>1.387181230882099</v>
       </c>
       <c r="E14">
-        <v>0.17672</v>
+        <v>0.20278</v>
       </c>
       <c r="F14">
-        <v>0.3127200000000001</v>
+        <v>0.33878</v>
       </c>
       <c r="G14">
         <v>1.23</v>
@@ -2417,28 +2417,28 @@
         <v>0.349</v>
       </c>
       <c r="M14">
-        <v>0.015729816</v>
+        <v>0.017040634</v>
       </c>
       <c r="N14">
-        <v>0.333270184</v>
+        <v>0.331959366</v>
       </c>
       <c r="O14">
-        <v>0.02999431656</v>
+        <v>0.02987634294</v>
       </c>
       <c r="P14">
-        <v>0.30327586744</v>
+        <v>0.30208302306</v>
       </c>
       <c r="Q14">
-        <v>0.33727586744</v>
+        <v>0.33608302306</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1194594896286118</v>
+        <v>0.120238362787022</v>
       </c>
       <c r="T14">
-        <v>1.071835325454713</v>
+        <v>1.08316887893766</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.18716353706871</v>
+        <v>20.48045864960189</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1105578656247091</v>
+        <v>0.1104986203762398</v>
       </c>
       <c r="C15">
-        <v>2.278401230882099</v>
+        <v>2.252760313189606</v>
       </c>
       <c r="D15">
-        <v>1.387181230882099</v>
+        <v>1.387600313189606</v>
       </c>
       <c r="E15">
-        <v>0.20278</v>
+        <v>0.22884</v>
       </c>
       <c r="F15">
-        <v>0.33878</v>
+        <v>0.3648400000000001</v>
       </c>
       <c r="G15">
         <v>1.23</v>
@@ -2499,28 +2499,28 @@
         <v>0.349</v>
       </c>
       <c r="M15">
-        <v>0.017040634</v>
+        <v>0.018351452</v>
       </c>
       <c r="N15">
-        <v>0.331959366</v>
+        <v>0.330648548</v>
       </c>
       <c r="O15">
-        <v>0.02987634294</v>
+        <v>0.02975836932</v>
       </c>
       <c r="P15">
-        <v>0.30208302306</v>
+        <v>0.30089017868</v>
       </c>
       <c r="Q15">
-        <v>0.33608302306</v>
+        <v>0.33489017868</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.120238362787022</v>
+        <v>0.1210353492746974</v>
       </c>
       <c r="T15">
-        <v>1.08316887893766</v>
+        <v>1.094766003431838</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.48045864960189</v>
+        <v>19.01756874605889</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1104986203762398</v>
+        <v>0.1104393751277704</v>
       </c>
       <c r="C16">
-        <v>2.252760313189606</v>
+        <v>2.227119648792144</v>
       </c>
       <c r="D16">
-        <v>1.387600313189606</v>
+        <v>1.388019648792144</v>
       </c>
       <c r="E16">
-        <v>0.22884</v>
+        <v>0.2549000000000001</v>
       </c>
       <c r="F16">
-        <v>0.3648400000000001</v>
+        <v>0.3909000000000001</v>
       </c>
       <c r="G16">
         <v>1.23</v>
@@ -2581,28 +2581,28 @@
         <v>0.349</v>
       </c>
       <c r="M16">
-        <v>0.018351452</v>
+        <v>0.01966227</v>
       </c>
       <c r="N16">
-        <v>0.330648548</v>
+        <v>0.32933773</v>
       </c>
       <c r="O16">
-        <v>0.02975836932</v>
+        <v>0.0296403957</v>
       </c>
       <c r="P16">
-        <v>0.30089017868</v>
+        <v>0.2996973343</v>
       </c>
       <c r="Q16">
-        <v>0.33489017868</v>
+        <v>0.3336973343</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1210353492746974</v>
+        <v>0.1218510883856123</v>
       </c>
       <c r="T16">
-        <v>1.094766003431838</v>
+        <v>1.106636001443526</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.01756874605889</v>
+        <v>17.74973082965496</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1104393751277704</v>
+        <v>0.1103801298793011</v>
       </c>
       <c r="C17">
-        <v>2.227119648792144</v>
+        <v>2.201479237919421</v>
       </c>
       <c r="D17">
-        <v>1.388019648792144</v>
+        <v>1.38843923791942</v>
       </c>
       <c r="E17">
-        <v>0.2549</v>
+        <v>0.28096</v>
       </c>
       <c r="F17">
-        <v>0.3909</v>
+        <v>0.4169600000000001</v>
       </c>
       <c r="G17">
         <v>1.23</v>
@@ -2663,28 +2663,28 @@
         <v>0.349</v>
       </c>
       <c r="M17">
-        <v>0.01966227</v>
+        <v>0.020973088</v>
       </c>
       <c r="N17">
-        <v>0.32933773</v>
+        <v>0.328026912</v>
       </c>
       <c r="O17">
-        <v>0.0296403957</v>
+        <v>0.02952242208</v>
       </c>
       <c r="P17">
-        <v>0.2996973343</v>
+        <v>0.29850448992</v>
       </c>
       <c r="Q17">
-        <v>0.3336973343</v>
+        <v>0.33250448992</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1218510883856123</v>
+        <v>0.1226862498563109</v>
       </c>
       <c r="T17">
-        <v>1.106636001443526</v>
+        <v>1.118788618455493</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.74973082965497</v>
+        <v>16.64037265280153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1103801298793011</v>
+        <v>0.1103208846308318</v>
       </c>
       <c r="C18">
-        <v>2.201479237919421</v>
+        <v>2.175839080801422</v>
       </c>
       <c r="D18">
-        <v>1.38843923791942</v>
+        <v>1.388859080801422</v>
       </c>
       <c r="E18">
-        <v>0.28096</v>
+        <v>0.3070200000000001</v>
       </c>
       <c r="F18">
-        <v>0.4169600000000001</v>
+        <v>0.4430200000000001</v>
       </c>
       <c r="G18">
         <v>1.23</v>
@@ -2745,28 +2745,28 @@
         <v>0.349</v>
       </c>
       <c r="M18">
-        <v>0.020973088</v>
+        <v>0.022283906</v>
       </c>
       <c r="N18">
-        <v>0.328026912</v>
+        <v>0.326716094</v>
       </c>
       <c r="O18">
-        <v>0.02952242208</v>
+        <v>0.02940444846</v>
       </c>
       <c r="P18">
-        <v>0.29850448992</v>
+        <v>0.2973116455399999</v>
       </c>
       <c r="Q18">
-        <v>0.33250448992</v>
+        <v>0.33131164554</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1226862498563109</v>
+        <v>0.1235415356997973</v>
       </c>
       <c r="T18">
-        <v>1.118788618455493</v>
+        <v>1.131234069612326</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.64037265280153</v>
+        <v>15.66152720263673</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1103208846308318</v>
+        <v>0.1102616393823624</v>
       </c>
       <c r="C19">
-        <v>2.175839080801422</v>
+        <v>2.150199177668413</v>
       </c>
       <c r="D19">
-        <v>1.388859080801422</v>
+        <v>1.389279177668413</v>
       </c>
       <c r="E19">
-        <v>0.3070200000000001</v>
+        <v>0.3330800000000001</v>
       </c>
       <c r="F19">
-        <v>0.4430200000000001</v>
+        <v>0.4690800000000001</v>
       </c>
       <c r="G19">
         <v>1.23</v>
@@ -2827,28 +2827,28 @@
         <v>0.349</v>
       </c>
       <c r="M19">
-        <v>0.022283906</v>
+        <v>0.023594724</v>
       </c>
       <c r="N19">
-        <v>0.326716094</v>
+        <v>0.325405276</v>
       </c>
       <c r="O19">
-        <v>0.02940444846</v>
+        <v>0.02928647484</v>
       </c>
       <c r="P19">
-        <v>0.2973116455399999</v>
+        <v>0.2961188011599999</v>
       </c>
       <c r="Q19">
-        <v>0.33131164554</v>
+        <v>0.33011880116</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1235415356997973</v>
+        <v>0.1244176821736127</v>
       </c>
       <c r="T19">
-        <v>1.131234069612326</v>
+        <v>1.14398306835835</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.66152720263673</v>
+        <v>14.7914423580458</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1102616393823625</v>
+        <v>0.1102023941338931</v>
       </c>
       <c r="C20">
-        <v>2.150199177668412</v>
+        <v>2.124559528750935</v>
       </c>
       <c r="D20">
-        <v>1.389279177668412</v>
+        <v>1.389699528750935</v>
       </c>
       <c r="E20">
-        <v>0.33308</v>
+        <v>0.3591400000000001</v>
       </c>
       <c r="F20">
-        <v>0.4690800000000001</v>
+        <v>0.4951400000000001</v>
       </c>
       <c r="G20">
         <v>1.23</v>
@@ -2909,28 +2909,28 @@
         <v>0.349</v>
       </c>
       <c r="M20">
-        <v>0.023594724</v>
+        <v>0.024905542</v>
       </c>
       <c r="N20">
-        <v>0.325405276</v>
+        <v>0.324094458</v>
       </c>
       <c r="O20">
-        <v>0.02928647484</v>
+        <v>0.02916850122</v>
       </c>
       <c r="P20">
-        <v>0.2961188011599999</v>
+        <v>0.29492595678</v>
       </c>
       <c r="Q20">
-        <v>0.33011880116</v>
+        <v>0.32892595678</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1244176821736127</v>
+        <v>0.1253154618936952</v>
       </c>
       <c r="T20">
-        <v>1.14398306835835</v>
+        <v>1.157046857196868</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.7914423580458</v>
+        <v>14.01294539183287</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1102023941338931</v>
+        <v>0.1101431488854238</v>
       </c>
       <c r="C21">
-        <v>2.124559528750935</v>
+        <v>2.098920134279813</v>
       </c>
       <c r="D21">
-        <v>1.389699528750935</v>
+        <v>1.390120134279813</v>
       </c>
       <c r="E21">
-        <v>0.3591400000000001</v>
+        <v>0.3852000000000001</v>
       </c>
       <c r="F21">
-        <v>0.4951400000000001</v>
+        <v>0.5212000000000001</v>
       </c>
       <c r="G21">
         <v>1.23</v>
@@ -2991,28 +2991,28 @@
         <v>0.349</v>
       </c>
       <c r="M21">
-        <v>0.024905542</v>
+        <v>0.02621636</v>
       </c>
       <c r="N21">
-        <v>0.324094458</v>
+        <v>0.32278364</v>
       </c>
       <c r="O21">
-        <v>0.02916850122</v>
+        <v>0.0290505276</v>
       </c>
       <c r="P21">
-        <v>0.29492595678</v>
+        <v>0.2937331124</v>
       </c>
       <c r="Q21">
-        <v>0.32892595678</v>
+        <v>0.3277331124</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1253154618936952</v>
+        <v>0.1262356861067797</v>
       </c>
       <c r="T21">
-        <v>1.157046857196868</v>
+        <v>1.17043724075635</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.01294539183287</v>
+        <v>13.31229812224122</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1101431488854238</v>
+        <v>0.1103705536369545</v>
       </c>
       <c r="C22">
-        <v>2.098920134279813</v>
+        <v>2.071247082992468</v>
       </c>
       <c r="D22">
-        <v>1.390120134279813</v>
+        <v>1.388507082992468</v>
       </c>
       <c r="E22">
-        <v>0.3852000000000001</v>
+        <v>0.4112600000000001</v>
       </c>
       <c r="F22">
-        <v>0.5212000000000001</v>
+        <v>0.5472600000000001</v>
       </c>
       <c r="G22">
         <v>1.23</v>
@@ -3073,45 +3073,45 @@
         <v>0.349</v>
       </c>
       <c r="M22">
-        <v>0.02621636</v>
+        <v>0.028348068</v>
       </c>
       <c r="N22">
-        <v>0.32278364</v>
+        <v>0.320651932</v>
       </c>
       <c r="O22">
-        <v>0.0290505276</v>
+        <v>0.02885867388</v>
       </c>
       <c r="P22">
-        <v>0.2937331124</v>
+        <v>0.29179325812</v>
       </c>
       <c r="Q22">
-        <v>0.3277331124</v>
+        <v>0.32579325812</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1262356861067797</v>
+        <v>0.1271792071353854</v>
       </c>
       <c r="T22">
-        <v>1.17043724075635</v>
+        <v>1.18416662136797</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.09</v>
       </c>
       <c r="W22">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.31229812224122</v>
+        <v>12.31124463226206</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1103705536369545</v>
+        <v>0.1103249583884851</v>
       </c>
       <c r="C23">
-        <v>2.071247082992468</v>
+        <v>2.045510203890507</v>
       </c>
       <c r="D23">
-        <v>1.388507082992468</v>
+        <v>1.388830203890507</v>
       </c>
       <c r="E23">
-        <v>0.4112600000000001</v>
+        <v>0.43732</v>
       </c>
       <c r="F23">
-        <v>0.5472600000000001</v>
+        <v>0.5733200000000001</v>
       </c>
       <c r="G23">
         <v>1.23</v>
@@ -3155,28 +3155,28 @@
         <v>0.349</v>
       </c>
       <c r="M23">
-        <v>0.028348068</v>
+        <v>0.029697976</v>
       </c>
       <c r="N23">
-        <v>0.320651932</v>
+        <v>0.319302024</v>
       </c>
       <c r="O23">
-        <v>0.02885867388</v>
+        <v>0.02873718216</v>
       </c>
       <c r="P23">
-        <v>0.29179325812</v>
+        <v>0.29056484184</v>
       </c>
       <c r="Q23">
-        <v>0.32579325812</v>
+        <v>0.32456484184</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1271792071353854</v>
+        <v>0.1281469210108784</v>
       </c>
       <c r="T23">
-        <v>1.18416662136797</v>
+        <v>1.198248037379888</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.31124463226206</v>
+        <v>11.75164260352288</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1103249583884851</v>
+        <v>0.1102793631400158</v>
       </c>
       <c r="C24">
-        <v>2.045510203890507</v>
+        <v>2.019773475211137</v>
       </c>
       <c r="D24">
-        <v>1.388830203890507</v>
+        <v>1.389153475211137</v>
       </c>
       <c r="E24">
-        <v>0.43732</v>
+        <v>0.4633800000000001</v>
       </c>
       <c r="F24">
-        <v>0.5733200000000001</v>
+        <v>0.5993800000000001</v>
       </c>
       <c r="G24">
         <v>1.23</v>
@@ -3237,28 +3237,28 @@
         <v>0.349</v>
       </c>
       <c r="M24">
-        <v>0.029697976</v>
+        <v>0.031047884</v>
       </c>
       <c r="N24">
-        <v>0.319302024</v>
+        <v>0.317952116</v>
       </c>
       <c r="O24">
-        <v>0.02873718216</v>
+        <v>0.02861569043999999</v>
       </c>
       <c r="P24">
-        <v>0.29056484184</v>
+        <v>0.2893364255599999</v>
       </c>
       <c r="Q24">
-        <v>0.32456484184</v>
+        <v>0.32333642556</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1281469210108784</v>
+        <v>0.1291397703117088</v>
       </c>
       <c r="T24">
-        <v>1.198248037379888</v>
+        <v>1.212695204457051</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.75164260352288</v>
+        <v>11.24070162076101</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1102793631400158</v>
+        <v>0.1102337678915465</v>
       </c>
       <c r="C25">
-        <v>2.019773475211137</v>
+        <v>1.994036897059423</v>
       </c>
       <c r="D25">
-        <v>1.389153475211137</v>
+        <v>1.389476897059423</v>
       </c>
       <c r="E25">
-        <v>0.4633800000000001</v>
+        <v>0.4894400000000001</v>
       </c>
       <c r="F25">
-        <v>0.5993800000000001</v>
+        <v>0.6254400000000001</v>
       </c>
       <c r="G25">
         <v>1.23</v>
@@ -3319,28 +3319,28 @@
         <v>0.349</v>
       </c>
       <c r="M25">
-        <v>0.031047884</v>
+        <v>0.032397792</v>
       </c>
       <c r="N25">
-        <v>0.317952116</v>
+        <v>0.316602208</v>
       </c>
       <c r="O25">
-        <v>0.02861569043999999</v>
+        <v>0.02849419872</v>
       </c>
       <c r="P25">
-        <v>0.2893364255599999</v>
+        <v>0.28810800928</v>
       </c>
       <c r="Q25">
-        <v>0.32333642556</v>
+        <v>0.3221080092800001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1291397703117088</v>
+        <v>0.130158747225719</v>
       </c>
       <c r="T25">
-        <v>1.212695204457051</v>
+        <v>1.227522560141508</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.24070162076101</v>
+        <v>10.77233905322931</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1102337678915465</v>
+        <v>0.1101881726430771</v>
       </c>
       <c r="C26">
-        <v>1.994036897059423</v>
+        <v>1.968300469540527</v>
       </c>
       <c r="D26">
-        <v>1.389476897059423</v>
+        <v>1.389800469540527</v>
       </c>
       <c r="E26">
-        <v>0.4894400000000001</v>
+        <v>0.5155000000000001</v>
       </c>
       <c r="F26">
-        <v>0.6254400000000001</v>
+        <v>0.6515000000000001</v>
       </c>
       <c r="G26">
         <v>1.23</v>
@@ -3401,28 +3401,28 @@
         <v>0.349</v>
       </c>
       <c r="M26">
-        <v>0.032397792</v>
+        <v>0.03374770000000001</v>
       </c>
       <c r="N26">
-        <v>0.316602208</v>
+        <v>0.3152523</v>
       </c>
       <c r="O26">
-        <v>0.02849419872</v>
+        <v>0.028372707</v>
       </c>
       <c r="P26">
-        <v>0.28810800928</v>
+        <v>0.286879593</v>
       </c>
       <c r="Q26">
-        <v>0.3221080092800001</v>
+        <v>0.320879593</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.130158747225719</v>
+        <v>0.1312048968574362</v>
       </c>
       <c r="T26">
-        <v>1.227522560141508</v>
+        <v>1.24274531197755</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.77233905322931</v>
+        <v>10.34144549110013</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1101881726430771</v>
+        <v>0.1101425773946078</v>
       </c>
       <c r="C27">
-        <v>1.968300469540527</v>
+        <v>1.942564192759707</v>
       </c>
       <c r="D27">
-        <v>1.389800469540527</v>
+        <v>1.390124192759707</v>
       </c>
       <c r="E27">
-        <v>0.5155000000000001</v>
+        <v>0.54156</v>
       </c>
       <c r="F27">
-        <v>0.6515000000000001</v>
+        <v>0.6775600000000001</v>
       </c>
       <c r="G27">
         <v>1.23</v>
@@ -3483,28 +3483,28 @@
         <v>0.349</v>
       </c>
       <c r="M27">
-        <v>0.03374770000000001</v>
+        <v>0.035097608</v>
       </c>
       <c r="N27">
-        <v>0.3152523</v>
+        <v>0.313902392</v>
       </c>
       <c r="O27">
-        <v>0.028372707</v>
+        <v>0.02825121528</v>
       </c>
       <c r="P27">
-        <v>0.286879593</v>
+        <v>0.28565117672</v>
       </c>
       <c r="Q27">
-        <v>0.320879593</v>
+        <v>0.31965117672</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1312048968574362</v>
+        <v>0.1322793208035241</v>
       </c>
       <c r="T27">
-        <v>1.24274531197755</v>
+        <v>1.258379489538891</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.34144549110013</v>
+        <v>9.943697587596281</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1101425773946078</v>
+        <v>0.1105146721461385</v>
       </c>
       <c r="C28">
-        <v>1.942564192759707</v>
+        <v>1.913866742996273</v>
       </c>
       <c r="D28">
-        <v>1.390124192759707</v>
+        <v>1.387486742996273</v>
       </c>
       <c r="E28">
-        <v>0.54156</v>
+        <v>0.5676200000000001</v>
       </c>
       <c r="F28">
-        <v>0.6775600000000001</v>
+        <v>0.7036200000000001</v>
       </c>
       <c r="G28">
         <v>1.23</v>
@@ -3565,45 +3565,45 @@
         <v>0.349</v>
       </c>
       <c r="M28">
-        <v>0.035097608</v>
+        <v>0.03764367</v>
       </c>
       <c r="N28">
-        <v>0.313902392</v>
+        <v>0.31135633</v>
       </c>
       <c r="O28">
-        <v>0.02825121528</v>
+        <v>0.0280220697</v>
       </c>
       <c r="P28">
-        <v>0.28565117672</v>
+        <v>0.2833342603</v>
       </c>
       <c r="Q28">
-        <v>0.31965117672</v>
+        <v>0.3173342603</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1322793208035241</v>
+        <v>0.1333831810221075</v>
       </c>
       <c r="T28">
-        <v>1.258379489538891</v>
+        <v>1.274442000732049</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.09</v>
       </c>
       <c r="W28">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.943697587596281</v>
+        <v>9.271147048095999</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1105146721461385</v>
+        <v>0.1104845468976692</v>
       </c>
       <c r="C29">
-        <v>1.913866742996273</v>
+        <v>1.888019901785903</v>
       </c>
       <c r="D29">
-        <v>1.387486742996273</v>
+        <v>1.387699901785903</v>
       </c>
       <c r="E29">
-        <v>0.5676200000000001</v>
+        <v>0.5936800000000001</v>
       </c>
       <c r="F29">
-        <v>0.7036200000000001</v>
+        <v>0.7296800000000001</v>
       </c>
       <c r="G29">
         <v>1.23</v>
@@ -3647,28 +3647,28 @@
         <v>0.349</v>
       </c>
       <c r="M29">
-        <v>0.03764367</v>
+        <v>0.03903788</v>
       </c>
       <c r="N29">
-        <v>0.31135633</v>
+        <v>0.30996212</v>
       </c>
       <c r="O29">
-        <v>0.0280220697</v>
+        <v>0.0278965908</v>
       </c>
       <c r="P29">
-        <v>0.2833342603</v>
+        <v>0.2820655291999999</v>
       </c>
       <c r="Q29">
-        <v>0.3173342603</v>
+        <v>0.3160655292</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1333831810221075</v>
+        <v>0.1345177040245405</v>
       </c>
       <c r="T29">
-        <v>1.274442000732049</v>
+        <v>1.290950692791684</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.271147048095999</v>
+        <v>8.940034653521142</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1104845468976692</v>
+        <v>0.1104544216491998</v>
       </c>
       <c r="C30">
-        <v>1.888019901785903</v>
+        <v>1.86217312608052</v>
       </c>
       <c r="D30">
-        <v>1.387699901785903</v>
+        <v>1.38791312608052</v>
       </c>
       <c r="E30">
-        <v>0.5936800000000001</v>
+        <v>0.6197400000000002</v>
       </c>
       <c r="F30">
-        <v>0.7296800000000001</v>
+        <v>0.7557400000000002</v>
       </c>
       <c r="G30">
         <v>1.23</v>
@@ -3729,28 +3729,28 @@
         <v>0.349</v>
       </c>
       <c r="M30">
-        <v>0.03903788</v>
+        <v>0.04043209000000001</v>
       </c>
       <c r="N30">
-        <v>0.30996212</v>
+        <v>0.3085679099999999</v>
       </c>
       <c r="O30">
-        <v>0.0278965908</v>
+        <v>0.0277711119</v>
       </c>
       <c r="P30">
-        <v>0.2820655291999999</v>
+        <v>0.2807967981</v>
       </c>
       <c r="Q30">
-        <v>0.3160655292</v>
+        <v>0.3147967981</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1345177040245405</v>
+        <v>0.1356841854214082</v>
       </c>
       <c r="T30">
-        <v>1.290950692791684</v>
+        <v>1.307924418430463</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.940034653521142</v>
+        <v>8.631757596503171</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1104544216491998</v>
+        <v>0.1104242964007305</v>
       </c>
       <c r="C31">
-        <v>1.86217312608052</v>
+        <v>1.836326415910326</v>
       </c>
       <c r="D31">
-        <v>1.38791312608052</v>
+        <v>1.388126415910326</v>
       </c>
       <c r="E31">
-        <v>0.6197400000000001</v>
+        <v>0.6458</v>
       </c>
       <c r="F31">
-        <v>0.7557400000000001</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="G31">
         <v>1.23</v>
@@ -3811,28 +3811,28 @@
         <v>0.349</v>
       </c>
       <c r="M31">
-        <v>0.04043209</v>
+        <v>0.0418263</v>
       </c>
       <c r="N31">
-        <v>0.3085679099999999</v>
+        <v>0.3071737</v>
       </c>
       <c r="O31">
-        <v>0.0277711119</v>
+        <v>0.027645633</v>
       </c>
       <c r="P31">
-        <v>0.2807967981</v>
+        <v>0.279528067</v>
       </c>
       <c r="Q31">
-        <v>0.3147967981</v>
+        <v>0.313528067</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1356841854214082</v>
+        <v>0.1368839948581864</v>
       </c>
       <c r="T31">
-        <v>1.307924418430463</v>
+        <v>1.325383107658922</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.631757596503171</v>
+        <v>8.344032343286401</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1104242964007305</v>
+        <v>0.1103941711522612</v>
       </c>
       <c r="C32">
-        <v>1.836326415910326</v>
+        <v>1.810479771305536</v>
       </c>
       <c r="D32">
-        <v>1.388126415910326</v>
+        <v>1.388339771305537</v>
       </c>
       <c r="E32">
-        <v>0.6458</v>
+        <v>0.6718600000000001</v>
       </c>
       <c r="F32">
-        <v>0.7818000000000001</v>
+        <v>0.8078600000000001</v>
       </c>
       <c r="G32">
         <v>1.23</v>
@@ -3893,28 +3893,28 @@
         <v>0.349</v>
       </c>
       <c r="M32">
-        <v>0.0418263</v>
+        <v>0.04322051</v>
       </c>
       <c r="N32">
-        <v>0.3071737</v>
+        <v>0.30577949</v>
       </c>
       <c r="O32">
-        <v>0.027645633</v>
+        <v>0.0275201541</v>
       </c>
       <c r="P32">
-        <v>0.279528067</v>
+        <v>0.2782593359</v>
       </c>
       <c r="Q32">
-        <v>0.313528067</v>
+        <v>0.3122593359</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1368839948581864</v>
+        <v>0.1381185813800886</v>
       </c>
       <c r="T32">
-        <v>1.325383107658922</v>
+        <v>1.343347845850524</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.344032343286401</v>
+        <v>8.074870009632001</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1103941711522612</v>
+        <v>0.1103640459037918</v>
       </c>
       <c r="C33">
-        <v>1.810479771305536</v>
+        <v>1.784633192296391</v>
       </c>
       <c r="D33">
-        <v>1.388339771305537</v>
+        <v>1.388553192296391</v>
       </c>
       <c r="E33">
-        <v>0.6718600000000001</v>
+        <v>0.6979200000000001</v>
       </c>
       <c r="F33">
-        <v>0.8078600000000001</v>
+        <v>0.8339200000000001</v>
       </c>
       <c r="G33">
         <v>1.23</v>
@@ -3975,28 +3975,28 @@
         <v>0.349</v>
       </c>
       <c r="M33">
-        <v>0.04322051</v>
+        <v>0.04461472</v>
       </c>
       <c r="N33">
-        <v>0.30577949</v>
+        <v>0.30438528</v>
       </c>
       <c r="O33">
-        <v>0.0275201541</v>
+        <v>0.0273946752</v>
       </c>
       <c r="P33">
-        <v>0.2782593359</v>
+        <v>0.2769906048</v>
       </c>
       <c r="Q33">
-        <v>0.3122593359</v>
+        <v>0.3109906048</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1381185813800886</v>
+        <v>0.1393894792702821</v>
       </c>
       <c r="T33">
-        <v>1.343347845850524</v>
+        <v>1.361840958694821</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.074870009632001</v>
+        <v>7.822530321831</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1103640459037918</v>
+        <v>0.1105741606553225</v>
       </c>
       <c r="C34">
-        <v>1.784633192296391</v>
+        <v>1.757086009329739</v>
       </c>
       <c r="D34">
-        <v>1.388553192296391</v>
+        <v>1.38706600932974</v>
       </c>
       <c r="E34">
-        <v>0.6979200000000001</v>
+        <v>0.7239800000000002</v>
       </c>
       <c r="F34">
-        <v>0.8339200000000001</v>
+        <v>0.8599800000000002</v>
       </c>
       <c r="G34">
         <v>1.23</v>
@@ -4057,45 +4057,45 @@
         <v>0.349</v>
       </c>
       <c r="M34">
-        <v>0.04461472</v>
+        <v>0.04669691400000001</v>
       </c>
       <c r="N34">
-        <v>0.30438528</v>
+        <v>0.3023030859999999</v>
       </c>
       <c r="O34">
-        <v>0.0273946752</v>
+        <v>0.02720727773999999</v>
       </c>
       <c r="P34">
-        <v>0.2769906048</v>
+        <v>0.27509580826</v>
       </c>
       <c r="Q34">
-        <v>0.3109906048</v>
+        <v>0.30909580826</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1393894792702821</v>
+        <v>0.1406983144109291</v>
       </c>
       <c r="T34">
-        <v>1.361840958694821</v>
+        <v>1.38088610475835</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.09</v>
       </c>
       <c r="W34">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.822530321831</v>
+        <v>7.473727278851872</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1105741606553225</v>
+        <v>0.1105513154068532</v>
       </c>
       <c r="C35">
-        <v>1.757086009329739</v>
+        <v>1.731187552621899</v>
       </c>
       <c r="D35">
-        <v>1.38706600932974</v>
+        <v>1.387227552621899</v>
       </c>
       <c r="E35">
-        <v>0.7239800000000002</v>
+        <v>0.7500400000000002</v>
       </c>
       <c r="F35">
-        <v>0.8599800000000002</v>
+        <v>0.8860400000000002</v>
       </c>
       <c r="G35">
         <v>1.23</v>
@@ -4139,28 +4139,28 @@
         <v>0.349</v>
       </c>
       <c r="M35">
-        <v>0.04669691400000001</v>
+        <v>0.04811197200000001</v>
       </c>
       <c r="N35">
-        <v>0.3023030859999999</v>
+        <v>0.300888028</v>
       </c>
       <c r="O35">
-        <v>0.02720727773999999</v>
+        <v>0.02707992252</v>
       </c>
       <c r="P35">
-        <v>0.27509580826</v>
+        <v>0.27380810548</v>
       </c>
       <c r="Q35">
-        <v>0.30909580826</v>
+        <v>0.30780810548</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1406983144109291</v>
+        <v>0.1420468112225048</v>
       </c>
       <c r="T35">
-        <v>1.38088610475835</v>
+        <v>1.400508376460169</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.473727278851872</v>
+        <v>7.253911770650347</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1105513154068532</v>
+        <v>0.1105284701583839</v>
       </c>
       <c r="C36">
-        <v>1.731187552621899</v>
+        <v>1.705289133546406</v>
       </c>
       <c r="D36">
-        <v>1.387227552621899</v>
+        <v>1.387389133546406</v>
       </c>
       <c r="E36">
-        <v>0.7500400000000002</v>
+        <v>0.7761000000000002</v>
       </c>
       <c r="F36">
-        <v>0.8860400000000002</v>
+        <v>0.9121000000000002</v>
       </c>
       <c r="G36">
         <v>1.23</v>
@@ -4221,28 +4221,28 @@
         <v>0.349</v>
       </c>
       <c r="M36">
-        <v>0.04811197200000001</v>
+        <v>0.04952703000000001</v>
       </c>
       <c r="N36">
-        <v>0.300888028</v>
+        <v>0.2994729699999999</v>
       </c>
       <c r="O36">
-        <v>0.02707992252</v>
+        <v>0.02695256729999999</v>
       </c>
       <c r="P36">
-        <v>0.27380810548</v>
+        <v>0.2725204026999999</v>
       </c>
       <c r="Q36">
-        <v>0.30780810548</v>
+        <v>0.3065204027</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1420468112225048</v>
+        <v>0.1434368002436675</v>
       </c>
       <c r="T36">
-        <v>1.400508376460169</v>
+        <v>1.420734410368197</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.253911770650347</v>
+        <v>7.046657148631764</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1105284701583839</v>
+        <v>0.1105056249099145</v>
       </c>
       <c r="C37">
-        <v>1.705289133546406</v>
+        <v>1.679390752116411</v>
       </c>
       <c r="D37">
-        <v>1.387389133546406</v>
+        <v>1.387550752116412</v>
       </c>
       <c r="E37">
-        <v>0.7761000000000002</v>
+        <v>0.8021600000000002</v>
       </c>
       <c r="F37">
-        <v>0.9121000000000002</v>
+        <v>0.9381600000000002</v>
       </c>
       <c r="G37">
         <v>1.23</v>
@@ -4303,28 +4303,28 @@
         <v>0.349</v>
       </c>
       <c r="M37">
-        <v>0.04952703000000001</v>
+        <v>0.05094208800000001</v>
       </c>
       <c r="N37">
-        <v>0.2994729699999999</v>
+        <v>0.298057912</v>
       </c>
       <c r="O37">
-        <v>0.02695256729999999</v>
+        <v>0.02682521208</v>
       </c>
       <c r="P37">
-        <v>0.2725204026999999</v>
+        <v>0.27123269992</v>
       </c>
       <c r="Q37">
-        <v>0.3065204027</v>
+        <v>0.30523269992</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1434368002436675</v>
+        <v>0.1448702264217414</v>
       </c>
       <c r="T37">
-        <v>1.420734410368197</v>
+        <v>1.441592507835851</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.046657148631764</v>
+        <v>6.850916672280883</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1105056249099145</v>
+        <v>0.1104827796614452</v>
       </c>
       <c r="C38">
-        <v>1.679390752116411</v>
+        <v>1.653492408345074</v>
       </c>
       <c r="D38">
-        <v>1.387550752116412</v>
+        <v>1.387712408345074</v>
       </c>
       <c r="E38">
-        <v>0.8021600000000001</v>
+        <v>0.8282200000000001</v>
       </c>
       <c r="F38">
-        <v>0.9381600000000001</v>
+        <v>0.9642200000000001</v>
       </c>
       <c r="G38">
         <v>1.23</v>
@@ -4385,28 +4385,28 @@
         <v>0.349</v>
       </c>
       <c r="M38">
-        <v>0.050942088</v>
+        <v>0.05235714600000001</v>
       </c>
       <c r="N38">
-        <v>0.298057912</v>
+        <v>0.296642854</v>
       </c>
       <c r="O38">
-        <v>0.02682521208</v>
+        <v>0.02669785685999999</v>
       </c>
       <c r="P38">
-        <v>0.27123269992</v>
+        <v>0.26994499714</v>
       </c>
       <c r="Q38">
-        <v>0.30523269992</v>
+        <v>0.30394499714</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1448702264217414</v>
+        <v>0.1463491581927701</v>
       </c>
       <c r="T38">
-        <v>1.44159250783585</v>
+        <v>1.463112767127875</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.850916672280884</v>
+        <v>6.665756762219238</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1104827796614452</v>
+        <v>0.1104599344129759</v>
       </c>
       <c r="C39">
-        <v>1.653492408345074</v>
+        <v>1.627594102245555</v>
       </c>
       <c r="D39">
-        <v>1.387712408345074</v>
+        <v>1.387874102245556</v>
       </c>
       <c r="E39">
-        <v>0.8282200000000001</v>
+        <v>0.8542800000000002</v>
       </c>
       <c r="F39">
-        <v>0.9642200000000001</v>
+        <v>0.9902800000000002</v>
       </c>
       <c r="G39">
         <v>1.23</v>
@@ -4467,28 +4467,28 @@
         <v>0.349</v>
       </c>
       <c r="M39">
-        <v>0.05235714600000001</v>
+        <v>0.05377220400000001</v>
       </c>
       <c r="N39">
-        <v>0.296642854</v>
+        <v>0.295227796</v>
       </c>
       <c r="O39">
-        <v>0.02669785685999999</v>
+        <v>0.02657050164</v>
       </c>
       <c r="P39">
-        <v>0.26994499714</v>
+        <v>0.26865729436</v>
       </c>
       <c r="Q39">
-        <v>0.30394499714</v>
+        <v>0.30265729436</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1463491581927701</v>
+        <v>0.1478757974402836</v>
       </c>
       <c r="T39">
-        <v>1.463112767127875</v>
+        <v>1.485327228332544</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.665756762219238</v>
+        <v>6.490342110581889</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1104599344129759</v>
+        <v>0.1104370891645065</v>
       </c>
       <c r="C40">
-        <v>1.627594102245555</v>
+        <v>1.601695833831028</v>
       </c>
       <c r="D40">
-        <v>1.387874102245556</v>
+        <v>1.388035833831028</v>
       </c>
       <c r="E40">
-        <v>0.8542800000000002</v>
+        <v>0.8803400000000002</v>
       </c>
       <c r="F40">
-        <v>0.9902800000000002</v>
+        <v>1.01634</v>
       </c>
       <c r="G40">
         <v>1.23</v>
@@ -4549,28 +4549,28 @@
         <v>0.349</v>
       </c>
       <c r="M40">
-        <v>0.05377220400000001</v>
+        <v>0.05518726200000001</v>
       </c>
       <c r="N40">
-        <v>0.295227796</v>
+        <v>0.293812738</v>
       </c>
       <c r="O40">
-        <v>0.02657050164</v>
+        <v>0.02644314642</v>
       </c>
       <c r="P40">
-        <v>0.26865729436</v>
+        <v>0.26736959158</v>
       </c>
       <c r="Q40">
-        <v>0.30265729436</v>
+        <v>0.30136959158</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1478757974402836</v>
+        <v>0.1494524904336172</v>
       </c>
       <c r="T40">
-        <v>1.485327228332544</v>
+        <v>1.508270032527531</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.490342110581889</v>
+        <v>6.32392308210543</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1104370891645065</v>
+        <v>0.1104142439160372</v>
       </c>
       <c r="C41">
-        <v>1.601695833831028</v>
+        <v>1.575797603114666</v>
       </c>
       <c r="D41">
-        <v>1.388035833831028</v>
+        <v>1.388197603114666</v>
       </c>
       <c r="E41">
-        <v>0.8803400000000002</v>
+        <v>0.9064000000000002</v>
       </c>
       <c r="F41">
-        <v>1.01634</v>
+        <v>1.0424</v>
       </c>
       <c r="G41">
         <v>1.23</v>
@@ -4631,28 +4631,28 @@
         <v>0.349</v>
       </c>
       <c r="M41">
-        <v>0.05518726200000001</v>
+        <v>0.05660232000000001</v>
       </c>
       <c r="N41">
-        <v>0.293812738</v>
+        <v>0.29239768</v>
       </c>
       <c r="O41">
-        <v>0.02644314642</v>
+        <v>0.0263157912</v>
       </c>
       <c r="P41">
-        <v>0.26736959158</v>
+        <v>0.2660818888</v>
       </c>
       <c r="Q41">
-        <v>0.30136959158</v>
+        <v>0.3000818888</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1494524904336172</v>
+        <v>0.151081739860062</v>
       </c>
       <c r="T41">
-        <v>1.508270032527531</v>
+        <v>1.531977596862351</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.32392308210543</v>
+        <v>6.165825005052795</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1104142439160372</v>
+        <v>0.1107644986675679</v>
       </c>
       <c r="C42">
-        <v>1.575797603114666</v>
+        <v>1.547261552571176</v>
       </c>
       <c r="D42">
-        <v>1.388197603114666</v>
+        <v>1.385721552571177</v>
       </c>
       <c r="E42">
-        <v>0.9064000000000002</v>
+        <v>0.9324600000000002</v>
       </c>
       <c r="F42">
-        <v>1.0424</v>
+        <v>1.06846</v>
       </c>
       <c r="G42">
         <v>1.23</v>
@@ -4713,45 +4713,45 @@
         <v>0.349</v>
       </c>
       <c r="M42">
-        <v>0.05660232000000001</v>
+        <v>0.05908583800000002</v>
       </c>
       <c r="N42">
-        <v>0.29239768</v>
+        <v>0.289914162</v>
       </c>
       <c r="O42">
-        <v>0.0263157912</v>
+        <v>0.02609227458</v>
       </c>
       <c r="P42">
-        <v>0.2660818888</v>
+        <v>0.26382188742</v>
       </c>
       <c r="Q42">
-        <v>0.3000818888</v>
+        <v>0.29782188742</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.151081739860062</v>
+        <v>0.1527662180806235</v>
       </c>
       <c r="T42">
-        <v>1.531977596862351</v>
+        <v>1.556488807445809</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.09</v>
       </c>
       <c r="W42">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.165825005052795</v>
+        <v>5.906660746691955</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1107644986675679</v>
+        <v>0.1107507534190985</v>
       </c>
       <c r="C43">
-        <v>1.547261552571176</v>
+        <v>1.521298555120178</v>
       </c>
       <c r="D43">
-        <v>1.385721552571177</v>
+        <v>1.385818555120178</v>
       </c>
       <c r="E43">
-        <v>0.9324600000000002</v>
+        <v>0.9585200000000001</v>
       </c>
       <c r="F43">
-        <v>1.06846</v>
+        <v>1.09452</v>
       </c>
       <c r="G43">
         <v>1.23</v>
@@ -4795,28 +4795,28 @@
         <v>0.349</v>
       </c>
       <c r="M43">
-        <v>0.05908583800000002</v>
+        <v>0.06052695600000001</v>
       </c>
       <c r="N43">
-        <v>0.289914162</v>
+        <v>0.288473044</v>
       </c>
       <c r="O43">
-        <v>0.02609227458</v>
+        <v>0.02596257396</v>
       </c>
       <c r="P43">
-        <v>0.26382188742</v>
+        <v>0.2625104700399999</v>
       </c>
       <c r="Q43">
-        <v>0.29782188742</v>
+        <v>0.29651047004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1527662180806235</v>
+        <v>0.1545087817570664</v>
       </c>
       <c r="T43">
-        <v>1.556488807445809</v>
+        <v>1.581845232187316</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.906660746691955</v>
+        <v>5.766025967008813</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1107507534190986</v>
+        <v>0.1107370081706292</v>
       </c>
       <c r="C44">
-        <v>1.521298555120178</v>
+        <v>1.495335571250773</v>
       </c>
       <c r="D44">
-        <v>1.385818555120178</v>
+        <v>1.385915571250773</v>
       </c>
       <c r="E44">
-        <v>0.9585200000000001</v>
+        <v>0.9845800000000001</v>
       </c>
       <c r="F44">
-        <v>1.09452</v>
+        <v>1.12058</v>
       </c>
       <c r="G44">
         <v>1.23</v>
@@ -4877,28 +4877,28 @@
         <v>0.349</v>
       </c>
       <c r="M44">
-        <v>0.06052695600000001</v>
+        <v>0.06196807400000001</v>
       </c>
       <c r="N44">
-        <v>0.288473044</v>
+        <v>0.2870319259999999</v>
       </c>
       <c r="O44">
-        <v>0.02596257396</v>
+        <v>0.02583287333999999</v>
       </c>
       <c r="P44">
-        <v>0.2625104700399999</v>
+        <v>0.2611990526599999</v>
       </c>
       <c r="Q44">
-        <v>0.29651047004</v>
+        <v>0.29519905266</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1545087817570664</v>
+        <v>0.1563124880186477</v>
       </c>
       <c r="T44">
-        <v>1.581845232187316</v>
+        <v>1.608091356042561</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.766025967008813</v>
+        <v>5.631932339869073</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1107370081706292</v>
+        <v>0.1107232629221599</v>
       </c>
       <c r="C45">
-        <v>1.495335571250773</v>
+        <v>1.469372600965813</v>
       </c>
       <c r="D45">
-        <v>1.385915571250773</v>
+        <v>1.386012600965814</v>
       </c>
       <c r="E45">
-        <v>0.9845800000000001</v>
+        <v>1.01064</v>
       </c>
       <c r="F45">
-        <v>1.12058</v>
+        <v>1.14664</v>
       </c>
       <c r="G45">
         <v>1.23</v>
@@ -4959,28 +4959,28 @@
         <v>0.349</v>
       </c>
       <c r="M45">
-        <v>0.06196807400000001</v>
+        <v>0.063409192</v>
       </c>
       <c r="N45">
-        <v>0.2870319259999999</v>
+        <v>0.285590808</v>
       </c>
       <c r="O45">
-        <v>0.02583287333999999</v>
+        <v>0.02570317272</v>
       </c>
       <c r="P45">
-        <v>0.2611990526599999</v>
+        <v>0.25988763528</v>
       </c>
       <c r="Q45">
-        <v>0.29519905266</v>
+        <v>0.29388763528</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1563124880186477</v>
+        <v>0.1581806123609998</v>
       </c>
       <c r="T45">
-        <v>1.608091356042561</v>
+        <v>1.635274841464065</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.631932339869073</v>
+        <v>5.503933877599323</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1107232629221599</v>
+        <v>0.1107095176736906</v>
       </c>
       <c r="C46">
-        <v>1.469372600965813</v>
+        <v>1.443409644268154</v>
       </c>
       <c r="D46">
-        <v>1.386012600965814</v>
+        <v>1.386109644268154</v>
       </c>
       <c r="E46">
-        <v>1.01064</v>
+        <v>1.0367</v>
       </c>
       <c r="F46">
-        <v>1.14664</v>
+        <v>1.1727</v>
       </c>
       <c r="G46">
         <v>1.23</v>
@@ -5041,28 +5041,28 @@
         <v>0.349</v>
       </c>
       <c r="M46">
-        <v>0.063409192</v>
+        <v>0.06485031000000001</v>
       </c>
       <c r="N46">
-        <v>0.285590808</v>
+        <v>0.28414969</v>
       </c>
       <c r="O46">
-        <v>0.02570317272</v>
+        <v>0.02557347209999999</v>
       </c>
       <c r="P46">
-        <v>0.25988763528</v>
+        <v>0.2585762179</v>
       </c>
       <c r="Q46">
-        <v>0.29388763528</v>
+        <v>0.2925762179</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1581806123609998</v>
+        <v>0.1601166684976192</v>
       </c>
       <c r="T46">
-        <v>1.635274841464065</v>
+        <v>1.663446817264533</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.503933877599323</v>
+        <v>5.381624235874892</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1107095176736906</v>
+        <v>0.1106957724252212</v>
       </c>
       <c r="C47">
-        <v>1.443409644268154</v>
+        <v>1.417446701160647</v>
       </c>
       <c r="D47">
-        <v>1.386109644268154</v>
+        <v>1.386206701160647</v>
       </c>
       <c r="E47">
-        <v>1.0367</v>
+        <v>1.06276</v>
       </c>
       <c r="F47">
-        <v>1.1727</v>
+        <v>1.19876</v>
       </c>
       <c r="G47">
         <v>1.23</v>
@@ -5123,28 +5123,28 @@
         <v>0.349</v>
       </c>
       <c r="M47">
-        <v>0.06485031000000001</v>
+        <v>0.06629142800000001</v>
       </c>
       <c r="N47">
-        <v>0.28414969</v>
+        <v>0.282708572</v>
       </c>
       <c r="O47">
-        <v>0.02557347209999999</v>
+        <v>0.02544377148</v>
       </c>
       <c r="P47">
-        <v>0.2585762179</v>
+        <v>0.25726480052</v>
       </c>
       <c r="Q47">
-        <v>0.2925762179</v>
+        <v>0.29126480052</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1601166684976192</v>
+        <v>0.1621244304170763</v>
       </c>
       <c r="T47">
-        <v>1.663446817264533</v>
+        <v>1.692662199576129</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.381624235874892</v>
+        <v>5.264632404660222</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1106957724252212</v>
+        <v>0.1106820271767519</v>
       </c>
       <c r="C48">
-        <v>1.417446701160647</v>
+        <v>1.391483771646149</v>
       </c>
       <c r="D48">
-        <v>1.386206701160647</v>
+        <v>1.386303771646149</v>
       </c>
       <c r="E48">
-        <v>1.06276</v>
+        <v>1.08882</v>
       </c>
       <c r="F48">
-        <v>1.19876</v>
+        <v>1.22482</v>
       </c>
       <c r="G48">
         <v>1.23</v>
@@ -5205,28 +5205,28 @@
         <v>0.349</v>
       </c>
       <c r="M48">
-        <v>0.06629142800000001</v>
+        <v>0.06773254600000002</v>
       </c>
       <c r="N48">
-        <v>0.282708572</v>
+        <v>0.281267454</v>
       </c>
       <c r="O48">
-        <v>0.02544377148</v>
+        <v>0.02531407086</v>
       </c>
       <c r="P48">
-        <v>0.25726480052</v>
+        <v>0.25595338314</v>
       </c>
       <c r="Q48">
-        <v>0.29126480052</v>
+        <v>0.28995338314</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1621244304170763</v>
+        <v>0.1642079569372678</v>
       </c>
       <c r="T48">
-        <v>1.692662199576129</v>
+        <v>1.722980049144766</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.264632404660222</v>
+        <v>5.152618949241918</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1106820271767519</v>
+        <v>0.1106682819282826</v>
       </c>
       <c r="C49">
-        <v>1.391483771646149</v>
+        <v>1.365520855727515</v>
       </c>
       <c r="D49">
-        <v>1.386303771646149</v>
+        <v>1.386400855727515</v>
       </c>
       <c r="E49">
-        <v>1.08882</v>
+        <v>1.11488</v>
       </c>
       <c r="F49">
-        <v>1.22482</v>
+        <v>1.25088</v>
       </c>
       <c r="G49">
         <v>1.23</v>
@@ -5287,28 +5287,28 @@
         <v>0.349</v>
       </c>
       <c r="M49">
-        <v>0.06773254600000002</v>
+        <v>0.06917366400000001</v>
       </c>
       <c r="N49">
-        <v>0.281267454</v>
+        <v>0.279826336</v>
       </c>
       <c r="O49">
-        <v>0.02531407086</v>
+        <v>0.02518437023999999</v>
       </c>
       <c r="P49">
-        <v>0.25595338314</v>
+        <v>0.25464196576</v>
       </c>
       <c r="Q49">
-        <v>0.28995338314</v>
+        <v>0.28864196576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1642079569372678</v>
+        <v>0.1663716190928511</v>
       </c>
       <c r="T49">
-        <v>1.722980049144766</v>
+        <v>1.754463969850659</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.152618949241918</v>
+        <v>5.045272721132712</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1106682819282826</v>
+        <v>0.1106545366798132</v>
       </c>
       <c r="C50">
-        <v>1.365520855727515</v>
+        <v>1.339557953407602</v>
       </c>
       <c r="D50">
-        <v>1.386400855727515</v>
+        <v>1.386497953407602</v>
       </c>
       <c r="E50">
-        <v>1.11488</v>
+        <v>1.14094</v>
       </c>
       <c r="F50">
-        <v>1.25088</v>
+        <v>1.27694</v>
       </c>
       <c r="G50">
         <v>1.23</v>
@@ -5369,28 +5369,28 @@
         <v>0.349</v>
       </c>
       <c r="M50">
-        <v>0.06917366400000001</v>
+        <v>0.07061478200000001</v>
       </c>
       <c r="N50">
-        <v>0.279826336</v>
+        <v>0.2783852179999999</v>
       </c>
       <c r="O50">
-        <v>0.02518437023999999</v>
+        <v>0.02505466961999999</v>
       </c>
       <c r="P50">
-        <v>0.25464196576</v>
+        <v>0.25333054838</v>
       </c>
       <c r="Q50">
-        <v>0.28864196576</v>
+        <v>0.28733054838</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1663716190928511</v>
+        <v>0.1686201307447318</v>
       </c>
       <c r="T50">
-        <v>1.754463969850659</v>
+        <v>1.787182554113645</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.045272721132712</v>
+        <v>4.94230797172184</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1106545366798132</v>
+        <v>0.1106407914313439</v>
       </c>
       <c r="C51">
-        <v>1.339557953407602</v>
+        <v>1.313595064689266</v>
       </c>
       <c r="D51">
-        <v>1.386497953407602</v>
+        <v>1.386595064689267</v>
       </c>
       <c r="E51">
-        <v>1.14094</v>
+        <v>1.167</v>
       </c>
       <c r="F51">
-        <v>1.27694</v>
+        <v>1.303</v>
       </c>
       <c r="G51">
         <v>1.23</v>
@@ -5451,28 +5451,28 @@
         <v>0.349</v>
       </c>
       <c r="M51">
-        <v>0.07061478200000001</v>
+        <v>0.07205590000000001</v>
       </c>
       <c r="N51">
-        <v>0.2783852179999999</v>
+        <v>0.2769441</v>
       </c>
       <c r="O51">
-        <v>0.02505466961999999</v>
+        <v>0.02492496899999999</v>
       </c>
       <c r="P51">
-        <v>0.25333054838</v>
+        <v>0.252019131</v>
       </c>
       <c r="Q51">
-        <v>0.28733054838</v>
+        <v>0.286019131</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1686201307447318</v>
+        <v>0.1709585828626878</v>
       </c>
       <c r="T51">
-        <v>1.787182554113645</v>
+        <v>1.821209881747152</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.94230797172184</v>
+        <v>4.843461812287404</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1106407914313439</v>
+        <v>0.1106270461828746</v>
       </c>
       <c r="C52">
-        <v>1.313595064689266</v>
+        <v>1.287632189575368</v>
       </c>
       <c r="D52">
-        <v>1.386595064689267</v>
+        <v>1.386692189575368</v>
       </c>
       <c r="E52">
-        <v>1.167</v>
+        <v>1.19306</v>
       </c>
       <c r="F52">
-        <v>1.303</v>
+        <v>1.32906</v>
       </c>
       <c r="G52">
         <v>1.23</v>
@@ -5533,28 +5533,28 @@
         <v>0.349</v>
       </c>
       <c r="M52">
-        <v>0.07205590000000001</v>
+        <v>0.07349701800000001</v>
       </c>
       <c r="N52">
-        <v>0.2769441</v>
+        <v>0.275502982</v>
       </c>
       <c r="O52">
-        <v>0.02492496899999999</v>
+        <v>0.02479526838</v>
       </c>
       <c r="P52">
-        <v>0.252019131</v>
+        <v>0.2507077136199999</v>
       </c>
       <c r="Q52">
-        <v>0.286019131</v>
+        <v>0.28470771362</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1709585828626878</v>
+        <v>0.1733924820058665</v>
       </c>
       <c r="T52">
-        <v>1.821209881747152</v>
+        <v>1.856626079896311</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.843461812287404</v>
+        <v>4.748491972830788</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1106270461828746</v>
+        <v>0.1106133009344053</v>
       </c>
       <c r="C53">
-        <v>1.287632189575368</v>
+        <v>1.261669328068765</v>
       </c>
       <c r="D53">
-        <v>1.386692189575368</v>
+        <v>1.386789328068765</v>
       </c>
       <c r="E53">
-        <v>1.19306</v>
+        <v>1.21912</v>
       </c>
       <c r="F53">
-        <v>1.32906</v>
+        <v>1.35512</v>
       </c>
       <c r="G53">
         <v>1.23</v>
@@ -5615,28 +5615,28 @@
         <v>0.349</v>
       </c>
       <c r="M53">
-        <v>0.07349701800000001</v>
+        <v>0.074938136</v>
       </c>
       <c r="N53">
-        <v>0.275502982</v>
+        <v>0.274061864</v>
       </c>
       <c r="O53">
-        <v>0.02479526838</v>
+        <v>0.02466556776</v>
       </c>
       <c r="P53">
-        <v>0.2507077136199999</v>
+        <v>0.24939629624</v>
       </c>
       <c r="Q53">
-        <v>0.28470771362</v>
+        <v>0.28339629624</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1733924820058665</v>
+        <v>0.1759277936133443</v>
       </c>
       <c r="T53">
-        <v>1.856626079896311</v>
+        <v>1.893517952968352</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.748491972830788</v>
+        <v>4.657174819507119</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1106133009344053</v>
+        <v>0.1105995556859359</v>
       </c>
       <c r="C54">
-        <v>1.261669328068765</v>
+        <v>1.235706480172317</v>
       </c>
       <c r="D54">
-        <v>1.386789328068765</v>
+        <v>1.386886480172317</v>
       </c>
       <c r="E54">
-        <v>1.21912</v>
+        <v>1.24518</v>
       </c>
       <c r="F54">
-        <v>1.35512</v>
+        <v>1.38118</v>
       </c>
       <c r="G54">
         <v>1.23</v>
@@ -5697,28 +5697,28 @@
         <v>0.349</v>
       </c>
       <c r="M54">
-        <v>0.074938136</v>
+        <v>0.07637925400000002</v>
       </c>
       <c r="N54">
-        <v>0.274061864</v>
+        <v>0.272620746</v>
       </c>
       <c r="O54">
-        <v>0.02466556776</v>
+        <v>0.02453586714</v>
       </c>
       <c r="P54">
-        <v>0.24939629624</v>
+        <v>0.24808487886</v>
       </c>
       <c r="Q54">
-        <v>0.28339629624</v>
+        <v>0.28208487886</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1759277936133443</v>
+        <v>0.1785709908211403</v>
       </c>
       <c r="T54">
-        <v>1.893517952968352</v>
+        <v>1.931979692979628</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.657174819507119</v>
+        <v>4.56930359649755</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1105995556859359</v>
+        <v>0.1118143104374666</v>
       </c>
       <c r="C55">
-        <v>1.235706480172317</v>
+        <v>1.201112765634775</v>
       </c>
       <c r="D55">
-        <v>1.386886480172317</v>
+        <v>1.378352765634775</v>
       </c>
       <c r="E55">
-        <v>1.24518</v>
+        <v>1.27124</v>
       </c>
       <c r="F55">
-        <v>1.38118</v>
+        <v>1.40724</v>
       </c>
       <c r="G55">
         <v>1.23</v>
@@ -5779,45 +5779,45 @@
         <v>0.349</v>
       </c>
       <c r="M55">
-        <v>0.07637925400000002</v>
+        <v>0.08133847200000002</v>
       </c>
       <c r="N55">
-        <v>0.272620746</v>
+        <v>0.267661528</v>
       </c>
       <c r="O55">
-        <v>0.02453586714</v>
+        <v>0.02408953752</v>
       </c>
       <c r="P55">
-        <v>0.24808487886</v>
+        <v>0.24357199048</v>
       </c>
       <c r="Q55">
-        <v>0.28208487886</v>
+        <v>0.27757199048</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1785709908211403</v>
+        <v>0.1813291096466665</v>
       </c>
       <c r="T55">
-        <v>1.931979692979628</v>
+        <v>1.972113682556613</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.09</v>
       </c>
       <c r="W55">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.56930359649755</v>
+        <v>4.290712517933702</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1118143104374666</v>
+        <v>0.1118233151889973</v>
       </c>
       <c r="C56">
-        <v>1.201112765634775</v>
+        <v>1.174989898901009</v>
       </c>
       <c r="D56">
-        <v>1.378352765634775</v>
+        <v>1.378289898901009</v>
       </c>
       <c r="E56">
-        <v>1.27124</v>
+        <v>1.2973</v>
       </c>
       <c r="F56">
-        <v>1.40724</v>
+        <v>1.4333</v>
       </c>
       <c r="G56">
         <v>1.23</v>
@@ -5861,28 +5861,28 @@
         <v>0.349</v>
       </c>
       <c r="M56">
-        <v>0.08133847200000002</v>
+        <v>0.08284474000000001</v>
       </c>
       <c r="N56">
-        <v>0.267661528</v>
+        <v>0.2661552599999999</v>
       </c>
       <c r="O56">
-        <v>0.02408953752</v>
+        <v>0.02395397339999999</v>
       </c>
       <c r="P56">
-        <v>0.24357199048</v>
+        <v>0.2422012866</v>
       </c>
       <c r="Q56">
-        <v>0.27757199048</v>
+        <v>0.2762012866</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1813291096466665</v>
+        <v>0.184209811531105</v>
       </c>
       <c r="T56">
-        <v>1.972113682556613</v>
+        <v>2.014031405003685</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.290712517933702</v>
+        <v>4.212699563062181</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1118233151889973</v>
+        <v>0.1118323199405279</v>
       </c>
       <c r="C57">
-        <v>1.174989898901009</v>
+        <v>1.14886703790169</v>
       </c>
       <c r="D57">
-        <v>1.378289898901009</v>
+        <v>1.37822703790169</v>
       </c>
       <c r="E57">
-        <v>1.2973</v>
+        <v>1.32336</v>
       </c>
       <c r="F57">
-        <v>1.4333</v>
+        <v>1.45936</v>
       </c>
       <c r="G57">
         <v>1.23</v>
@@ -5943,28 +5943,28 @@
         <v>0.349</v>
       </c>
       <c r="M57">
-        <v>0.08284474000000001</v>
+        <v>0.08435100800000002</v>
       </c>
       <c r="N57">
-        <v>0.2661552599999999</v>
+        <v>0.264648992</v>
       </c>
       <c r="O57">
-        <v>0.02395397339999999</v>
+        <v>0.02381840928</v>
       </c>
       <c r="P57">
-        <v>0.2422012866</v>
+        <v>0.24083058272</v>
       </c>
       <c r="Q57">
-        <v>0.2762012866</v>
+        <v>0.27483058272</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.184209811531105</v>
+        <v>0.1872214544102908</v>
       </c>
       <c r="T57">
-        <v>2.014031405003685</v>
+        <v>2.057854478471079</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.212699563062181</v>
+        <v>4.137472785150355</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1118323199405279</v>
+        <v>0.1118413246920586</v>
       </c>
       <c r="C58">
-        <v>1.14886703790169</v>
+        <v>1.122744182636034</v>
       </c>
       <c r="D58">
-        <v>1.37822703790169</v>
+        <v>1.378164182636035</v>
       </c>
       <c r="E58">
-        <v>1.32336</v>
+        <v>1.34942</v>
       </c>
       <c r="F58">
-        <v>1.45936</v>
+        <v>1.48542</v>
       </c>
       <c r="G58">
         <v>1.23</v>
@@ -6025,28 +6025,28 @@
         <v>0.349</v>
       </c>
       <c r="M58">
-        <v>0.08435100800000002</v>
+        <v>0.08585727600000002</v>
       </c>
       <c r="N58">
-        <v>0.264648992</v>
+        <v>0.2631427239999999</v>
       </c>
       <c r="O58">
-        <v>0.02381840928</v>
+        <v>0.02368284515999999</v>
       </c>
       <c r="P58">
-        <v>0.24083058272</v>
+        <v>0.2394598788399999</v>
       </c>
       <c r="Q58">
-        <v>0.27483058272</v>
+        <v>0.27345987884</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1872214544102908</v>
+        <v>0.1903731737024619</v>
       </c>
       <c r="T58">
-        <v>2.057854478471079</v>
+        <v>2.103715834425329</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.137472785150355</v>
+        <v>4.064885543305612</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1118413246920586</v>
+        <v>0.1136976294435893</v>
       </c>
       <c r="C59">
-        <v>1.122744182636034</v>
+        <v>1.083848013109621</v>
       </c>
       <c r="D59">
-        <v>1.378164182636035</v>
+        <v>1.365328013109621</v>
       </c>
       <c r="E59">
-        <v>1.34942</v>
+        <v>1.37548</v>
       </c>
       <c r="F59">
-        <v>1.48542</v>
+        <v>1.51148</v>
       </c>
       <c r="G59">
         <v>1.23</v>
@@ -6107,45 +6107,45 @@
         <v>0.349</v>
       </c>
       <c r="M59">
-        <v>0.08585727600000002</v>
+        <v>0.09265372400000002</v>
       </c>
       <c r="N59">
-        <v>0.2631427239999999</v>
+        <v>0.2563462759999999</v>
       </c>
       <c r="O59">
-        <v>0.02368284515999999</v>
+        <v>0.02307116483999999</v>
       </c>
       <c r="P59">
-        <v>0.2394598788399999</v>
+        <v>0.2332751111599999</v>
       </c>
       <c r="Q59">
-        <v>0.27345987884</v>
+        <v>0.26727511116</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1903731737024619</v>
+        <v>0.1936749748656888</v>
       </c>
       <c r="T59">
-        <v>2.103715834425329</v>
+        <v>2.151761064472638</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.09</v>
       </c>
       <c r="W59">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.064885543305612</v>
+        <v>3.766713143661661</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1136976294435893</v>
+        <v>0.1137384841951199</v>
       </c>
       <c r="C60">
-        <v>1.083848013109621</v>
+        <v>1.057508195032601</v>
       </c>
       <c r="D60">
-        <v>1.365328013109621</v>
+        <v>1.365048195032601</v>
       </c>
       <c r="E60">
-        <v>1.37548</v>
+        <v>1.40154</v>
       </c>
       <c r="F60">
-        <v>1.51148</v>
+        <v>1.53754</v>
       </c>
       <c r="G60">
         <v>1.23</v>
@@ -6189,28 +6189,28 @@
         <v>0.349</v>
       </c>
       <c r="M60">
-        <v>0.09265372400000001</v>
+        <v>0.09425120200000001</v>
       </c>
       <c r="N60">
-        <v>0.256346276</v>
+        <v>0.2547487979999999</v>
       </c>
       <c r="O60">
-        <v>0.02307116484</v>
+        <v>0.02292739181999999</v>
       </c>
       <c r="P60">
-        <v>0.23327511116</v>
+        <v>0.2318214061799999</v>
       </c>
       <c r="Q60">
-        <v>0.26727511116</v>
+        <v>0.2658214061799999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1936749748656888</v>
+        <v>0.1971378395002925</v>
       </c>
       <c r="T60">
-        <v>2.151761064472638</v>
+        <v>2.202149964278352</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.766713143661662</v>
+        <v>3.702870548006379</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1137384841951199</v>
+        <v>0.1137793389466506</v>
       </c>
       <c r="C61">
-        <v>1.057508195032601</v>
+        <v>1.031168491627092</v>
       </c>
       <c r="D61">
-        <v>1.365048195032601</v>
+        <v>1.364768491627092</v>
       </c>
       <c r="E61">
-        <v>1.40154</v>
+        <v>1.4276</v>
       </c>
       <c r="F61">
-        <v>1.53754</v>
+        <v>1.5636</v>
       </c>
       <c r="G61">
         <v>1.23</v>
@@ -6271,28 +6271,28 @@
         <v>0.349</v>
       </c>
       <c r="M61">
-        <v>0.09425120200000001</v>
+        <v>0.09584868000000001</v>
       </c>
       <c r="N61">
-        <v>0.2547487979999999</v>
+        <v>0.25315132</v>
       </c>
       <c r="O61">
-        <v>0.02292739181999999</v>
+        <v>0.0227836188</v>
       </c>
       <c r="P61">
-        <v>0.2318214061799999</v>
+        <v>0.2303677012</v>
       </c>
       <c r="Q61">
-        <v>0.2658214061799999</v>
+        <v>0.2643677012</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1971378395002925</v>
+        <v>0.2007738473666265</v>
       </c>
       <c r="T61">
-        <v>2.202149964278352</v>
+        <v>2.255058309074352</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.702870548006379</v>
+        <v>3.64115603887294</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1137793389466506</v>
+        <v>0.1138201936981813</v>
       </c>
       <c r="C62">
-        <v>1.031168491627092</v>
+        <v>1.004828902822618</v>
       </c>
       <c r="D62">
-        <v>1.364768491627092</v>
+        <v>1.364488902822618</v>
       </c>
       <c r="E62">
-        <v>1.4276</v>
+        <v>1.45366</v>
       </c>
       <c r="F62">
-        <v>1.5636</v>
+        <v>1.58966</v>
       </c>
       <c r="G62">
         <v>1.23</v>
@@ -6353,28 +6353,28 @@
         <v>0.349</v>
       </c>
       <c r="M62">
-        <v>0.09584868000000001</v>
+        <v>0.097446158</v>
       </c>
       <c r="N62">
-        <v>0.25315132</v>
+        <v>0.251553842</v>
       </c>
       <c r="O62">
-        <v>0.0227836188</v>
+        <v>0.02263984578</v>
       </c>
       <c r="P62">
-        <v>0.2303677012</v>
+        <v>0.22891399622</v>
       </c>
       <c r="Q62">
-        <v>0.2643677012</v>
+        <v>0.26291399622</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2007738473666265</v>
+        <v>0.2045963171748238</v>
       </c>
       <c r="T62">
-        <v>2.255058309074352</v>
+        <v>2.31067990232143</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.64115603887294</v>
+        <v>3.581464956268465</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1138201936981813</v>
+        <v>0.113861048449712</v>
       </c>
       <c r="C63">
-        <v>1.004828902822618</v>
+        <v>0.97848942854876</v>
       </c>
       <c r="D63">
-        <v>1.364488902822618</v>
+        <v>1.36420942854876</v>
       </c>
       <c r="E63">
-        <v>1.45366</v>
+        <v>1.47972</v>
       </c>
       <c r="F63">
-        <v>1.58966</v>
+        <v>1.61572</v>
       </c>
       <c r="G63">
         <v>1.23</v>
@@ -6435,28 +6435,28 @@
         <v>0.349</v>
       </c>
       <c r="M63">
-        <v>0.097446158</v>
+        <v>0.09904363600000002</v>
       </c>
       <c r="N63">
-        <v>0.251553842</v>
+        <v>0.249956364</v>
       </c>
       <c r="O63">
-        <v>0.02263984578</v>
+        <v>0.02249607276</v>
       </c>
       <c r="P63">
-        <v>0.22891399622</v>
+        <v>0.22746029124</v>
       </c>
       <c r="Q63">
-        <v>0.26291399622</v>
+        <v>0.26146029124</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2045963171748238</v>
+        <v>0.2086199696045052</v>
       </c>
       <c r="T63">
-        <v>2.31067990232143</v>
+        <v>2.369228947844669</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.581464956268465</v>
+        <v>3.523699392457683</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.113861048449712</v>
+        <v>0.1155071432012426</v>
       </c>
       <c r="C64">
-        <v>0.97848942854876</v>
+        <v>0.9412634745021986</v>
       </c>
       <c r="D64">
-        <v>1.36420942854876</v>
+        <v>1.353043474502199</v>
       </c>
       <c r="E64">
-        <v>1.47972</v>
+        <v>1.50578</v>
       </c>
       <c r="F64">
-        <v>1.61572</v>
+        <v>1.64178</v>
       </c>
       <c r="G64">
         <v>1.23</v>
@@ -6517,45 +6517,45 @@
         <v>0.349</v>
       </c>
       <c r="M64">
-        <v>0.09904363600000002</v>
+        <v>0.105238098</v>
       </c>
       <c r="N64">
-        <v>0.249956364</v>
+        <v>0.243761902</v>
       </c>
       <c r="O64">
-        <v>0.02249607276</v>
+        <v>0.02193857118</v>
       </c>
       <c r="P64">
-        <v>0.22746029124</v>
+        <v>0.22182333082</v>
       </c>
       <c r="Q64">
-        <v>0.26146029124</v>
+        <v>0.25582333082</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2086199696045052</v>
+        <v>0.2128611167601152</v>
       </c>
       <c r="T64">
-        <v>2.369228947844669</v>
+        <v>2.430942806639434</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.09</v>
       </c>
       <c r="W64">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.523699392457683</v>
+        <v>3.316289505726338</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1155071432012426</v>
+        <v>0.1155734779527733</v>
       </c>
       <c r="C65">
-        <v>0.9412634745021986</v>
+        <v>0.9147573361142178</v>
       </c>
       <c r="D65">
-        <v>1.353043474502199</v>
+        <v>1.352597336114218</v>
       </c>
       <c r="E65">
-        <v>1.50578</v>
+        <v>1.53184</v>
       </c>
       <c r="F65">
-        <v>1.64178</v>
+        <v>1.66784</v>
       </c>
       <c r="G65">
         <v>1.23</v>
@@ -6599,28 +6599,28 @@
         <v>0.349</v>
       </c>
       <c r="M65">
-        <v>0.105238098</v>
+        <v>0.106908544</v>
       </c>
       <c r="N65">
-        <v>0.243761902</v>
+        <v>0.242091456</v>
       </c>
       <c r="O65">
-        <v>0.02193857118</v>
+        <v>0.02178823103999999</v>
       </c>
       <c r="P65">
-        <v>0.22182333082</v>
+        <v>0.22030322496</v>
       </c>
       <c r="Q65">
-        <v>0.25582333082</v>
+        <v>0.25430322496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2128611167601152</v>
+        <v>0.2173378832021481</v>
       </c>
       <c r="T65">
-        <v>2.430942806639434</v>
+        <v>2.49608521314502</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.316289505726338</v>
+        <v>3.264472482199364</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1155734779527733</v>
+        <v>0.115639812704304</v>
       </c>
       <c r="C66">
-        <v>0.9147573361142178</v>
+        <v>0.8882514918392612</v>
       </c>
       <c r="D66">
-        <v>1.352597336114218</v>
+        <v>1.352151491839261</v>
       </c>
       <c r="E66">
-        <v>1.53184</v>
+        <v>1.5579</v>
       </c>
       <c r="F66">
-        <v>1.66784</v>
+        <v>1.6939</v>
       </c>
       <c r="G66">
         <v>1.23</v>
@@ -6681,28 +6681,28 @@
         <v>0.349</v>
       </c>
       <c r="M66">
-        <v>0.106908544</v>
+        <v>0.10857899</v>
       </c>
       <c r="N66">
-        <v>0.242091456</v>
+        <v>0.24042101</v>
       </c>
       <c r="O66">
-        <v>0.02178823103999999</v>
+        <v>0.02163789089999999</v>
       </c>
       <c r="P66">
-        <v>0.22030322496</v>
+        <v>0.2187831191</v>
       </c>
       <c r="Q66">
-        <v>0.25430322496</v>
+        <v>0.2527831191</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2173378832021481</v>
+        <v>0.22207046486944</v>
       </c>
       <c r="T66">
-        <v>2.49608521314502</v>
+        <v>2.564950042879496</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.264472482199364</v>
+        <v>3.214249828627066</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.115639812704304</v>
+        <v>0.1157061474558347</v>
       </c>
       <c r="C67">
-        <v>0.8882514918392612</v>
+        <v>0.861745941386586</v>
       </c>
       <c r="D67">
-        <v>1.352151491839261</v>
+        <v>1.351705941386586</v>
       </c>
       <c r="E67">
-        <v>1.5579</v>
+        <v>1.58396</v>
       </c>
       <c r="F67">
-        <v>1.6939</v>
+        <v>1.71996</v>
       </c>
       <c r="G67">
         <v>1.23</v>
@@ -6763,28 +6763,28 @@
         <v>0.349</v>
       </c>
       <c r="M67">
-        <v>0.10857899</v>
+        <v>0.110249436</v>
       </c>
       <c r="N67">
-        <v>0.24042101</v>
+        <v>0.2387505639999999</v>
       </c>
       <c r="O67">
-        <v>0.02163789089999999</v>
+        <v>0.02148755075999999</v>
       </c>
       <c r="P67">
-        <v>0.2187831191</v>
+        <v>0.2172630132399999</v>
       </c>
       <c r="Q67">
-        <v>0.2527831191</v>
+        <v>0.25126301324</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.22207046486944</v>
+        <v>0.2270814336936313</v>
       </c>
       <c r="T67">
-        <v>2.564950042879496</v>
+        <v>2.637865744951295</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.214249828627066</v>
+        <v>3.165549073647868</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1157061474558347</v>
+        <v>0.1157724822073653</v>
       </c>
       <c r="C68">
-        <v>0.861745941386586</v>
+        <v>0.8352406844658347</v>
       </c>
       <c r="D68">
-        <v>1.351705941386586</v>
+        <v>1.351260684465835</v>
       </c>
       <c r="E68">
-        <v>1.58396</v>
+        <v>1.61002</v>
       </c>
       <c r="F68">
-        <v>1.71996</v>
+        <v>1.74602</v>
       </c>
       <c r="G68">
         <v>1.23</v>
@@ -6845,28 +6845,28 @@
         <v>0.349</v>
       </c>
       <c r="M68">
-        <v>0.110249436</v>
+        <v>0.111919882</v>
       </c>
       <c r="N68">
-        <v>0.2387505639999999</v>
+        <v>0.237080118</v>
       </c>
       <c r="O68">
-        <v>0.02148755075999999</v>
+        <v>0.02133721061999999</v>
       </c>
       <c r="P68">
-        <v>0.2172630132399999</v>
+        <v>0.21574290738</v>
       </c>
       <c r="Q68">
-        <v>0.25126301324</v>
+        <v>0.24974290738</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2270814336936313</v>
+        <v>0.2323960975980768</v>
       </c>
       <c r="T68">
-        <v>2.637865744951295</v>
+        <v>2.71520058048199</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.165549073647868</v>
+        <v>3.118302072548646</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1157724822073653</v>
+        <v>0.115838816958896</v>
       </c>
       <c r="C69">
-        <v>0.8352406844658347</v>
+        <v>0.8087357207870314</v>
       </c>
       <c r="D69">
-        <v>1.351260684465835</v>
+        <v>1.350815720787032</v>
       </c>
       <c r="E69">
-        <v>1.61002</v>
+        <v>1.63608</v>
       </c>
       <c r="F69">
-        <v>1.74602</v>
+        <v>1.77208</v>
       </c>
       <c r="G69">
         <v>1.23</v>
@@ -6927,28 +6927,28 @@
         <v>0.349</v>
       </c>
       <c r="M69">
-        <v>0.111919882</v>
+        <v>0.113590328</v>
       </c>
       <c r="N69">
-        <v>0.237080118</v>
+        <v>0.235409672</v>
       </c>
       <c r="O69">
-        <v>0.02133721061999999</v>
+        <v>0.02118687047999999</v>
       </c>
       <c r="P69">
-        <v>0.21574290738</v>
+        <v>0.21422280152</v>
       </c>
       <c r="Q69">
-        <v>0.24974290738</v>
+        <v>0.24822280152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2323960975980768</v>
+        <v>0.23804292799655</v>
       </c>
       <c r="T69">
-        <v>2.71520058048199</v>
+        <v>2.797368843233354</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.118302072548646</v>
+        <v>3.072444689128813</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.115838816958896</v>
+        <v>0.1159051517104267</v>
       </c>
       <c r="C70">
-        <v>0.8087357207870314</v>
+        <v>0.7822310500605816</v>
       </c>
       <c r="D70">
-        <v>1.350815720787032</v>
+        <v>1.350371050060582</v>
       </c>
       <c r="E70">
-        <v>1.63608</v>
+        <v>1.66214</v>
       </c>
       <c r="F70">
-        <v>1.77208</v>
+        <v>1.79814</v>
       </c>
       <c r="G70">
         <v>1.23</v>
@@ -7009,28 +7009,28 @@
         <v>0.349</v>
       </c>
       <c r="M70">
-        <v>0.113590328</v>
+        <v>0.115260774</v>
       </c>
       <c r="N70">
-        <v>0.235409672</v>
+        <v>0.233739226</v>
       </c>
       <c r="O70">
-        <v>0.02118687047999999</v>
+        <v>0.02103653033999999</v>
       </c>
       <c r="P70">
-        <v>0.21422280152</v>
+        <v>0.21270269566</v>
       </c>
       <c r="Q70">
-        <v>0.24822280152</v>
+        <v>0.24670269566</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.23804292799655</v>
+        <v>0.2440540700336344</v>
       </c>
       <c r="T70">
-        <v>2.797368843233354</v>
+        <v>2.884838284226741</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.072444689128813</v>
+        <v>3.027916505228395</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1159051517104267</v>
+        <v>0.1209400864619573</v>
       </c>
       <c r="C71">
-        <v>0.7822310500605816</v>
+        <v>0.7232532807751262</v>
       </c>
       <c r="D71">
-        <v>1.350371050060582</v>
+        <v>1.317453280775127</v>
       </c>
       <c r="E71">
-        <v>1.66214</v>
+        <v>1.688200000000001</v>
       </c>
       <c r="F71">
-        <v>1.79814</v>
+        <v>1.8242</v>
       </c>
       <c r="G71">
         <v>1.23</v>
@@ -7091,45 +7091,45 @@
         <v>0.349</v>
       </c>
       <c r="M71">
-        <v>0.115260774</v>
+        <v>0.13115998</v>
       </c>
       <c r="N71">
-        <v>0.233739226</v>
+        <v>0.2178400199999999</v>
       </c>
       <c r="O71">
-        <v>0.02103653033999999</v>
+        <v>0.01960560179999999</v>
       </c>
       <c r="P71">
-        <v>0.21270269566</v>
+        <v>0.1982344182</v>
       </c>
       <c r="Q71">
-        <v>0.24670269566</v>
+        <v>0.2322344182</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2440540700336344</v>
+        <v>0.2504659548731911</v>
       </c>
       <c r="T71">
-        <v>2.884838284226741</v>
+        <v>2.978139021286355</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.09</v>
       </c>
       <c r="W71">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.027916505228395</v>
+        <v>2.6608726228839</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1209400864619573</v>
+        <v>0.121077401213488</v>
       </c>
       <c r="C72">
-        <v>0.7232532807751262</v>
+        <v>0.6963180003404812</v>
       </c>
       <c r="D72">
-        <v>1.317453280775127</v>
+        <v>1.316578000340482</v>
       </c>
       <c r="E72">
-        <v>1.688200000000001</v>
+        <v>1.71426</v>
       </c>
       <c r="F72">
-        <v>1.8242</v>
+        <v>1.85026</v>
       </c>
       <c r="G72">
         <v>1.23</v>
@@ -7173,28 +7173,28 @@
         <v>0.349</v>
       </c>
       <c r="M72">
-        <v>0.13115998</v>
+        <v>0.133033694</v>
       </c>
       <c r="N72">
-        <v>0.2178400199999999</v>
+        <v>0.2159663059999999</v>
       </c>
       <c r="O72">
-        <v>0.01960560179999999</v>
+        <v>0.01943696754</v>
       </c>
       <c r="P72">
-        <v>0.1982344182</v>
+        <v>0.19652933846</v>
       </c>
       <c r="Q72">
-        <v>0.2322344182</v>
+        <v>0.23052933846</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2504659548731911</v>
+        <v>0.2573200386672</v>
       </c>
       <c r="T72">
-        <v>2.978139021286355</v>
+        <v>3.077874291936286</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.6608726228839</v>
+        <v>2.623395543688352</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.121077401213488</v>
+        <v>0.1212147159650187</v>
       </c>
       <c r="C73">
-        <v>0.6963180003404819</v>
+        <v>0.6693838821591052</v>
       </c>
       <c r="D73">
-        <v>1.316578000340482</v>
+        <v>1.315703882159105</v>
       </c>
       <c r="E73">
-        <v>1.71426</v>
+        <v>1.74032</v>
       </c>
       <c r="F73">
-        <v>1.85026</v>
+        <v>1.87632</v>
       </c>
       <c r="G73">
         <v>1.23</v>
@@ -7255,28 +7255,28 @@
         <v>0.349</v>
       </c>
       <c r="M73">
-        <v>0.133033694</v>
+        <v>0.134907408</v>
       </c>
       <c r="N73">
-        <v>0.2159663059999999</v>
+        <v>0.2140925919999999</v>
       </c>
       <c r="O73">
-        <v>0.01943696754</v>
+        <v>0.01926833327999999</v>
       </c>
       <c r="P73">
-        <v>0.19652933846</v>
+        <v>0.1948242587199999</v>
       </c>
       <c r="Q73">
-        <v>0.23052933846</v>
+        <v>0.22882425872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2573200386671999</v>
+        <v>0.2646636998750667</v>
       </c>
       <c r="T73">
-        <v>3.077874291936285</v>
+        <v>3.184733510489783</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.623395543688352</v>
+        <v>2.586959494470459</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1212147159650187</v>
+        <v>0.1213520307165493</v>
       </c>
       <c r="C74">
-        <v>0.6693838821591052</v>
+        <v>0.6424509239175611</v>
       </c>
       <c r="D74">
-        <v>1.315703882159105</v>
+        <v>1.314830923917561</v>
       </c>
       <c r="E74">
-        <v>1.74032</v>
+        <v>1.76638</v>
       </c>
       <c r="F74">
-        <v>1.87632</v>
+        <v>1.90238</v>
       </c>
       <c r="G74">
         <v>1.23</v>
@@ -7337,28 +7337,28 @@
         <v>0.349</v>
       </c>
       <c r="M74">
-        <v>0.134907408</v>
+        <v>0.136781122</v>
       </c>
       <c r="N74">
-        <v>0.2140925919999999</v>
+        <v>0.2122188779999999</v>
       </c>
       <c r="O74">
-        <v>0.01926833327999999</v>
+        <v>0.01909969902</v>
       </c>
       <c r="P74">
-        <v>0.1948242587199999</v>
+        <v>0.1931191789799999</v>
       </c>
       <c r="Q74">
-        <v>0.22882425872</v>
+        <v>0.22711917898</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2646636998750667</v>
+        <v>0.2725513359872198</v>
       </c>
       <c r="T74">
-        <v>3.184733510489783</v>
+        <v>3.29950822671391</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.586959494470459</v>
+        <v>2.551521693176343</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1213520307165493</v>
+        <v>0.12148934546808</v>
       </c>
       <c r="C75">
-        <v>0.6424509239175611</v>
+        <v>0.61551912330855</v>
       </c>
       <c r="D75">
-        <v>1.314830923917561</v>
+        <v>1.31395912330855</v>
       </c>
       <c r="E75">
-        <v>1.76638</v>
+        <v>1.79244</v>
       </c>
       <c r="F75">
-        <v>1.90238</v>
+        <v>1.92844</v>
       </c>
       <c r="G75">
         <v>1.23</v>
@@ -7419,28 +7419,28 @@
         <v>0.349</v>
       </c>
       <c r="M75">
-        <v>0.136781122</v>
+        <v>0.138654836</v>
       </c>
       <c r="N75">
-        <v>0.2122188779999999</v>
+        <v>0.2103451639999999</v>
       </c>
       <c r="O75">
-        <v>0.01909969902</v>
+        <v>0.01893106475999999</v>
       </c>
       <c r="P75">
-        <v>0.1931191789799999</v>
+        <v>0.1914140992399999</v>
       </c>
       <c r="Q75">
-        <v>0.22711917898</v>
+        <v>0.22541409924</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2725513359872198</v>
+        <v>0.2810457133387693</v>
       </c>
       <c r="T75">
-        <v>3.29950822671391</v>
+        <v>3.423111767262971</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.551521693176343</v>
+        <v>2.517041670295582</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.12148934546808</v>
+        <v>0.1242884102196107</v>
       </c>
       <c r="C76">
-        <v>0.61551912330855</v>
+        <v>0.5719366937532553</v>
       </c>
       <c r="D76">
-        <v>1.31395912330855</v>
+        <v>1.296436693753256</v>
       </c>
       <c r="E76">
-        <v>1.79244</v>
+        <v>1.8185</v>
       </c>
       <c r="F76">
-        <v>1.92844</v>
+        <v>1.9545</v>
       </c>
       <c r="G76">
         <v>1.23</v>
@@ -7501,45 +7501,45 @@
         <v>0.349</v>
       </c>
       <c r="M76">
-        <v>0.138654836</v>
+        <v>0.1481511</v>
       </c>
       <c r="N76">
-        <v>0.2103451639999999</v>
+        <v>0.2008488999999999</v>
       </c>
       <c r="O76">
-        <v>0.01893106475999999</v>
+        <v>0.018076401</v>
       </c>
       <c r="P76">
-        <v>0.1914140992399999</v>
+        <v>0.1827724989999999</v>
       </c>
       <c r="Q76">
-        <v>0.22541409924</v>
+        <v>0.216772499</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2810457133387693</v>
+        <v>0.2902196408784427</v>
       </c>
       <c r="T76">
-        <v>3.423111767262971</v>
+        <v>3.556603591055955</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.09</v>
       </c>
       <c r="W76">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.517041670295582</v>
+        <v>2.355703062616477</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1242884102196107</v>
+        <v>0.1244612149711413</v>
       </c>
       <c r="C77">
-        <v>0.5719366937532553</v>
+        <v>0.5448102226017768</v>
       </c>
       <c r="D77">
-        <v>1.296436693753256</v>
+        <v>1.295370222601777</v>
       </c>
       <c r="E77">
-        <v>1.8185</v>
+        <v>1.84456</v>
       </c>
       <c r="F77">
-        <v>1.9545</v>
+        <v>1.98056</v>
       </c>
       <c r="G77">
         <v>1.23</v>
@@ -7583,28 +7583,28 @@
         <v>0.349</v>
       </c>
       <c r="M77">
-        <v>0.1481511</v>
+        <v>0.150126448</v>
       </c>
       <c r="N77">
-        <v>0.2008488999999999</v>
+        <v>0.198873552</v>
       </c>
       <c r="O77">
-        <v>0.018076401</v>
+        <v>0.01789861967999999</v>
       </c>
       <c r="P77">
-        <v>0.1827724989999999</v>
+        <v>0.1809749323199999</v>
       </c>
       <c r="Q77">
-        <v>0.216772499</v>
+        <v>0.21497493232</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2902196408784427</v>
+        <v>0.3001580623797556</v>
       </c>
       <c r="T77">
-        <v>3.556603591055955</v>
+        <v>3.701219733498356</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.355703062616477</v>
+        <v>2.324706969687313</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1244612149711413</v>
+        <v>0.124634019722672</v>
       </c>
       <c r="C78">
-        <v>0.5448102226017768</v>
+        <v>0.5176855046031963</v>
       </c>
       <c r="D78">
-        <v>1.295370222601777</v>
+        <v>1.294305504603196</v>
       </c>
       <c r="E78">
-        <v>1.84456</v>
+        <v>1.87062</v>
       </c>
       <c r="F78">
-        <v>1.98056</v>
+        <v>2.00662</v>
       </c>
       <c r="G78">
         <v>1.23</v>
@@ -7665,28 +7665,28 @@
         <v>0.349</v>
       </c>
       <c r="M78">
-        <v>0.150126448</v>
+        <v>0.152101796</v>
       </c>
       <c r="N78">
-        <v>0.198873552</v>
+        <v>0.1968982039999999</v>
       </c>
       <c r="O78">
-        <v>0.01789861967999999</v>
+        <v>0.01772083835999999</v>
       </c>
       <c r="P78">
-        <v>0.1809749323199999</v>
+        <v>0.1791773656399999</v>
       </c>
       <c r="Q78">
-        <v>0.21497493232</v>
+        <v>0.21317736564</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3001580623797556</v>
+        <v>0.3109606944464001</v>
       </c>
       <c r="T78">
-        <v>3.701219733498356</v>
+        <v>3.858411192674879</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.324706969687313</v>
+        <v>2.294515970080984</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.124634019722672</v>
+        <v>0.1248068244742027</v>
       </c>
       <c r="C79">
-        <v>0.5176855046031963</v>
+        <v>0.4905625354380985</v>
       </c>
       <c r="D79">
-        <v>1.294305504603196</v>
+        <v>1.293242535438099</v>
       </c>
       <c r="E79">
-        <v>1.87062</v>
+        <v>1.89668</v>
       </c>
       <c r="F79">
-        <v>2.00662</v>
+        <v>2.03268</v>
       </c>
       <c r="G79">
         <v>1.23</v>
@@ -7747,28 +7747,28 @@
         <v>0.349</v>
       </c>
       <c r="M79">
-        <v>0.152101796</v>
+        <v>0.1540771440000001</v>
       </c>
       <c r="N79">
-        <v>0.1968982039999999</v>
+        <v>0.1949228559999999</v>
       </c>
       <c r="O79">
-        <v>0.01772083835999999</v>
+        <v>0.01754305703999999</v>
       </c>
       <c r="P79">
-        <v>0.1791773656399999</v>
+        <v>0.1773797989599999</v>
       </c>
       <c r="Q79">
-        <v>0.21317736564</v>
+        <v>0.2113797989599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3109606944464001</v>
+        <v>0.3227453839736486</v>
       </c>
       <c r="T79">
-        <v>3.858411192674879</v>
+        <v>4.029892784503811</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.294515970080984</v>
+        <v>2.265099098669689</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1248068244742027</v>
+        <v>0.1249796292257334</v>
       </c>
       <c r="C80">
-        <v>0.4905625354380985</v>
+        <v>0.4634413108012483</v>
       </c>
       <c r="D80">
-        <v>1.293242535438099</v>
+        <v>1.292181310801248</v>
       </c>
       <c r="E80">
-        <v>1.89668</v>
+        <v>1.92274</v>
       </c>
       <c r="F80">
-        <v>2.03268</v>
+        <v>2.05874</v>
       </c>
       <c r="G80">
         <v>1.23</v>
@@ -7829,28 +7829,28 @@
         <v>0.349</v>
       </c>
       <c r="M80">
-        <v>0.1540771440000001</v>
+        <v>0.156052492</v>
       </c>
       <c r="N80">
-        <v>0.1949228559999999</v>
+        <v>0.1929475079999999</v>
       </c>
       <c r="O80">
-        <v>0.01754305703999999</v>
+        <v>0.01736527571999999</v>
       </c>
       <c r="P80">
-        <v>0.1773797989599999</v>
+        <v>0.1755822322799999</v>
       </c>
       <c r="Q80">
-        <v>0.2113797989599999</v>
+        <v>0.20958223228</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3227453839736486</v>
+        <v>0.3356524248844446</v>
       </c>
       <c r="T80">
-        <v>4.029892784503811</v>
+        <v>4.217705956506928</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.265099098669689</v>
+        <v>2.236426958180199</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1249796292257334</v>
+        <v>0.1251524339772641</v>
       </c>
       <c r="C81">
-        <v>0.4634413108012483</v>
+        <v>0.4363218264015258</v>
       </c>
       <c r="D81">
-        <v>1.292181310801248</v>
+        <v>1.291121826401526</v>
       </c>
       <c r="E81">
-        <v>1.92274</v>
+        <v>1.9488</v>
       </c>
       <c r="F81">
-        <v>2.05874</v>
+        <v>2.0848</v>
       </c>
       <c r="G81">
         <v>1.23</v>
@@ -7911,28 +7911,28 @@
         <v>0.349</v>
       </c>
       <c r="M81">
-        <v>0.156052492</v>
+        <v>0.1580278400000001</v>
       </c>
       <c r="N81">
-        <v>0.1929475079999999</v>
+        <v>0.1909721599999999</v>
       </c>
       <c r="O81">
-        <v>0.01736527571999999</v>
+        <v>0.01718749439999999</v>
       </c>
       <c r="P81">
-        <v>0.1755822322799999</v>
+        <v>0.1737846655999999</v>
       </c>
       <c r="Q81">
-        <v>0.20958223228</v>
+        <v>0.2077846655999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3356524248844446</v>
+        <v>0.3498501698863202</v>
       </c>
       <c r="T81">
-        <v>4.217705956506928</v>
+        <v>4.424300445710358</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.236426958180199</v>
+        <v>2.208471621202946</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1251524339772641</v>
+        <v>0.1253252387287947</v>
       </c>
       <c r="C82">
-        <v>0.4363218264015258</v>
+        <v>0.4092040779618782</v>
       </c>
       <c r="D82">
-        <v>1.291121826401526</v>
+        <v>1.290064077961879</v>
       </c>
       <c r="E82">
-        <v>1.9488</v>
+        <v>1.97486</v>
       </c>
       <c r="F82">
-        <v>2.0848</v>
+        <v>2.11086</v>
       </c>
       <c r="G82">
         <v>1.23</v>
@@ -7993,28 +7993,28 @@
         <v>0.349</v>
       </c>
       <c r="M82">
-        <v>0.1580278400000001</v>
+        <v>0.160003188</v>
       </c>
       <c r="N82">
-        <v>0.1909721599999999</v>
+        <v>0.188996812</v>
       </c>
       <c r="O82">
-        <v>0.01718749439999999</v>
+        <v>0.01700971308</v>
       </c>
       <c r="P82">
-        <v>0.1737846655999999</v>
+        <v>0.17198709892</v>
       </c>
       <c r="Q82">
-        <v>0.2077846655999999</v>
+        <v>0.20598709892</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3498501698863202</v>
+        <v>0.3655424143620775</v>
       </c>
       <c r="T82">
-        <v>4.424300445710358</v>
+        <v>4.652641723250991</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.208471621202946</v>
+        <v>2.181206539459701</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1253252387287947</v>
+        <v>0.1254980434803254</v>
       </c>
       <c r="C83">
-        <v>0.4092040779618782</v>
+        <v>0.3820880612192536</v>
       </c>
       <c r="D83">
-        <v>1.290064077961879</v>
+        <v>1.289008061219254</v>
       </c>
       <c r="E83">
-        <v>1.97486</v>
+        <v>2.00092</v>
       </c>
       <c r="F83">
-        <v>2.11086</v>
+        <v>2.13692</v>
       </c>
       <c r="G83">
         <v>1.23</v>
@@ -8075,28 +8075,28 @@
         <v>0.349</v>
       </c>
       <c r="M83">
-        <v>0.160003188</v>
+        <v>0.161978536</v>
       </c>
       <c r="N83">
-        <v>0.188996812</v>
+        <v>0.1870214639999999</v>
       </c>
       <c r="O83">
-        <v>0.01700971308</v>
+        <v>0.01683193175999999</v>
       </c>
       <c r="P83">
-        <v>0.17198709892</v>
+        <v>0.1701895322399999</v>
       </c>
       <c r="Q83">
-        <v>0.20598709892</v>
+        <v>0.20418953224</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3655424143620775</v>
+        <v>0.3829782415573633</v>
       </c>
       <c r="T83">
-        <v>4.652641723250991</v>
+        <v>4.906354253851693</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.181206539459701</v>
+        <v>2.154606459710192</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1254980434803254</v>
+        <v>0.1256708482318561</v>
       </c>
       <c r="C84">
-        <v>0.3820880612192536</v>
+        <v>0.354973771924548</v>
       </c>
       <c r="D84">
-        <v>1.289008061219254</v>
+        <v>1.287953771924549</v>
       </c>
       <c r="E84">
-        <v>2.00092</v>
+        <v>2.02698</v>
       </c>
       <c r="F84">
-        <v>2.13692</v>
+        <v>2.162980000000001</v>
       </c>
       <c r="G84">
         <v>1.23</v>
@@ -8157,28 +8157,28 @@
         <v>0.349</v>
       </c>
       <c r="M84">
-        <v>0.161978536</v>
+        <v>0.163953884</v>
       </c>
       <c r="N84">
-        <v>0.1870214639999999</v>
+        <v>0.1850461159999999</v>
       </c>
       <c r="O84">
-        <v>0.01683193175999999</v>
+        <v>0.01665415043999999</v>
       </c>
       <c r="P84">
-        <v>0.1701895322399999</v>
+        <v>0.1683919655599999</v>
       </c>
       <c r="Q84">
-        <v>0.20418953224</v>
+        <v>0.20239196556</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3829782415573633</v>
+        <v>0.4024653425403298</v>
       </c>
       <c r="T84">
-        <v>4.906354253851693</v>
+        <v>5.189915317464243</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.154606459710192</v>
+        <v>2.12864734573778</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1256708482318561</v>
+        <v>0.1258436529833867</v>
       </c>
       <c r="C85">
-        <v>0.354973771924548</v>
+        <v>0.3278612058425496</v>
       </c>
       <c r="D85">
-        <v>1.287953771924549</v>
+        <v>1.28690120584255</v>
       </c>
       <c r="E85">
-        <v>2.02698</v>
+        <v>2.05304</v>
       </c>
       <c r="F85">
-        <v>2.162980000000001</v>
+        <v>2.18904</v>
       </c>
       <c r="G85">
         <v>1.23</v>
@@ -8239,28 +8239,28 @@
         <v>0.349</v>
       </c>
       <c r="M85">
-        <v>0.163953884</v>
+        <v>0.165929232</v>
       </c>
       <c r="N85">
-        <v>0.1850461159999999</v>
+        <v>0.1830707679999999</v>
       </c>
       <c r="O85">
-        <v>0.01665415043999999</v>
+        <v>0.01647636911999999</v>
       </c>
       <c r="P85">
-        <v>0.1683919655599999</v>
+        <v>0.1665943988799999</v>
       </c>
       <c r="Q85">
-        <v>0.20239196556</v>
+        <v>0.20059439888</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4024653425403298</v>
+        <v>0.4243883311461672</v>
       </c>
       <c r="T85">
-        <v>5.189915317464243</v>
+        <v>5.508921514028363</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.12864734573778</v>
+        <v>2.103306305907569</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1258436529833867</v>
+        <v>0.1260164577349174</v>
       </c>
       <c r="C86">
-        <v>0.3278612058425496</v>
+        <v>0.3007503587518765</v>
       </c>
       <c r="D86">
-        <v>1.28690120584255</v>
+        <v>1.285850358751876</v>
       </c>
       <c r="E86">
-        <v>2.05304</v>
+        <v>2.0791</v>
       </c>
       <c r="F86">
-        <v>2.18904</v>
+        <v>2.2151</v>
       </c>
       <c r="G86">
         <v>1.23</v>
@@ -8321,28 +8321,28 @@
         <v>0.349</v>
       </c>
       <c r="M86">
-        <v>0.165929232</v>
+        <v>0.16790458</v>
       </c>
       <c r="N86">
-        <v>0.1830707679999999</v>
+        <v>0.18109542</v>
       </c>
       <c r="O86">
-        <v>0.01647636911999999</v>
+        <v>0.0162985878</v>
       </c>
       <c r="P86">
-        <v>0.1665943988799999</v>
+        <v>0.1647968322</v>
       </c>
       <c r="Q86">
-        <v>0.20059439888</v>
+        <v>0.1987968322</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4243883311461669</v>
+        <v>0.4492343848994492</v>
       </c>
       <c r="T86">
-        <v>5.508921514028359</v>
+        <v>5.870461870134361</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.103306305907569</v>
+        <v>2.078561525838068</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1260164577349174</v>
+        <v>0.1261892624864481</v>
       </c>
       <c r="C87">
-        <v>0.3007503587518765</v>
+        <v>0.2736412264449255</v>
       </c>
       <c r="D87">
-        <v>1.285850358751876</v>
+        <v>1.284801226444926</v>
       </c>
       <c r="E87">
-        <v>2.0791</v>
+        <v>2.10516</v>
       </c>
       <c r="F87">
-        <v>2.2151</v>
+        <v>2.24116</v>
       </c>
       <c r="G87">
         <v>1.23</v>
@@ -8403,28 +8403,28 @@
         <v>0.349</v>
       </c>
       <c r="M87">
-        <v>0.16790458</v>
+        <v>0.169879928</v>
       </c>
       <c r="N87">
-        <v>0.18109542</v>
+        <v>0.1791200719999999</v>
       </c>
       <c r="O87">
-        <v>0.0162985878</v>
+        <v>0.01612080647999999</v>
       </c>
       <c r="P87">
-        <v>0.1647968322</v>
+        <v>0.1629992655199999</v>
       </c>
       <c r="Q87">
-        <v>0.1987968322</v>
+        <v>0.19699926552</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4492343848994492</v>
+        <v>0.4776298749032004</v>
       </c>
       <c r="T87">
-        <v>5.870461870134361</v>
+        <v>6.283650848541218</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.078561525838068</v>
+        <v>2.054392205770183</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1261892624864481</v>
+        <v>0.1263620672379787</v>
       </c>
       <c r="C88">
-        <v>0.2736412264449255</v>
+        <v>0.2465338047278149</v>
       </c>
       <c r="D88">
-        <v>1.284801226444926</v>
+        <v>1.283753804727815</v>
       </c>
       <c r="E88">
-        <v>2.10516</v>
+        <v>2.13122</v>
       </c>
       <c r="F88">
-        <v>2.24116</v>
+        <v>2.26722</v>
       </c>
       <c r="G88">
         <v>1.23</v>
@@ -8485,28 +8485,28 @@
         <v>0.349</v>
       </c>
       <c r="M88">
-        <v>0.169879928</v>
+        <v>0.1718552760000001</v>
       </c>
       <c r="N88">
-        <v>0.1791200719999999</v>
+        <v>0.1771447239999999</v>
       </c>
       <c r="O88">
-        <v>0.01612080647999999</v>
+        <v>0.01594302515999999</v>
       </c>
       <c r="P88">
-        <v>0.1629992655199999</v>
+        <v>0.1612016988399999</v>
       </c>
       <c r="Q88">
-        <v>0.19699926552</v>
+        <v>0.19520169884</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4776298749032004</v>
+        <v>0.5103939018306055</v>
       </c>
       <c r="T88">
-        <v>6.283650848541218</v>
+        <v>6.760407362087594</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.054392205770183</v>
+        <v>2.030778502255583</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1263620672379787</v>
+        <v>0.1265348719895094</v>
       </c>
       <c r="C89">
-        <v>0.2465338047278149</v>
+        <v>0.2194280894203278</v>
       </c>
       <c r="D89">
-        <v>1.283753804727815</v>
+        <v>1.282708089420328</v>
       </c>
       <c r="E89">
-        <v>2.13122</v>
+        <v>2.15728</v>
       </c>
       <c r="F89">
-        <v>2.26722</v>
+        <v>2.29328</v>
       </c>
       <c r="G89">
         <v>1.23</v>
@@ -8567,28 +8567,28 @@
         <v>0.349</v>
       </c>
       <c r="M89">
-        <v>0.1718552760000001</v>
+        <v>0.173830624</v>
       </c>
       <c r="N89">
-        <v>0.1771447239999999</v>
+        <v>0.175169376</v>
       </c>
       <c r="O89">
-        <v>0.01594302515999999</v>
+        <v>0.01576524383999999</v>
       </c>
       <c r="P89">
-        <v>0.1612016988399999</v>
+        <v>0.15940413216</v>
       </c>
       <c r="Q89">
-        <v>0.19520169884</v>
+        <v>0.19340413216</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5103939018306055</v>
+        <v>0.5486185999125782</v>
       </c>
       <c r="T89">
-        <v>6.760407362087594</v>
+        <v>7.316623294558364</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.030778502255583</v>
+        <v>2.007701473820861</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1265348719895094</v>
+        <v>0.13820825674104</v>
       </c>
       <c r="C90">
-        <v>0.2194280894203278</v>
+        <v>0.1264663734139759</v>
       </c>
       <c r="D90">
-        <v>1.282708089420328</v>
+        <v>1.215806373413976</v>
       </c>
       <c r="E90">
-        <v>2.15728</v>
+        <v>2.18334</v>
       </c>
       <c r="F90">
-        <v>2.29328</v>
+        <v>2.31934</v>
       </c>
       <c r="G90">
         <v>1.23</v>
@@ -8649,45 +8649,45 @@
         <v>0.349</v>
       </c>
       <c r="M90">
-        <v>0.173830624</v>
+        <v>0.2087406</v>
       </c>
       <c r="N90">
-        <v>0.175169376</v>
+        <v>0.1402594</v>
       </c>
       <c r="O90">
-        <v>0.01576524383999999</v>
+        <v>0.012623346</v>
       </c>
       <c r="P90">
-        <v>0.15940413216</v>
+        <v>0.1276360539999999</v>
       </c>
       <c r="Q90">
-        <v>0.19340413216</v>
+        <v>0.161636054</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5486185999125782</v>
+        <v>0.5937932431003642</v>
       </c>
       <c r="T90">
-        <v>7.316623294558364</v>
+        <v>7.973969396569275</v>
       </c>
       <c r="U90">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V90">
         <v>0.09</v>
       </c>
       <c r="W90">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.007701473820861</v>
+        <v>1.671931574403829</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.13820825674104</v>
+        <v>0.1385102814925707</v>
       </c>
       <c r="C91">
-        <v>0.1264663734139759</v>
+        <v>0.09876792069358276</v>
       </c>
       <c r="D91">
-        <v>1.215806373413976</v>
+        <v>1.214167920693583</v>
       </c>
       <c r="E91">
-        <v>2.18334</v>
+        <v>2.2094</v>
       </c>
       <c r="F91">
-        <v>2.31934</v>
+        <v>2.3454</v>
       </c>
       <c r="G91">
         <v>1.23</v>
@@ -8731,28 +8731,28 @@
         <v>0.349</v>
       </c>
       <c r="M91">
-        <v>0.2087406</v>
+        <v>0.211086</v>
       </c>
       <c r="N91">
-        <v>0.1402594</v>
+        <v>0.137914</v>
       </c>
       <c r="O91">
-        <v>0.012623346</v>
+        <v>0.01241226</v>
       </c>
       <c r="P91">
-        <v>0.1276360539999999</v>
+        <v>0.12550174</v>
       </c>
       <c r="Q91">
-        <v>0.161636054</v>
+        <v>0.15950174</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5937932431003642</v>
+        <v>0.6480028149257074</v>
       </c>
       <c r="T91">
-        <v>7.973969396569275</v>
+        <v>8.762784718982369</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.671931574403829</v>
+        <v>1.653354556910454</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1385102814925707</v>
+        <v>0.1388123062441014</v>
       </c>
       <c r="C92">
-        <v>0.09876792069358276</v>
+        <v>0.07107387807417975</v>
       </c>
       <c r="D92">
-        <v>1.214167920693583</v>
+        <v>1.21253387807418</v>
       </c>
       <c r="E92">
-        <v>2.2094</v>
+        <v>2.23546</v>
       </c>
       <c r="F92">
-        <v>2.3454</v>
+        <v>2.37146</v>
       </c>
       <c r="G92">
         <v>1.23</v>
@@ -8813,28 +8813,28 @@
         <v>0.349</v>
       </c>
       <c r="M92">
-        <v>0.211086</v>
+        <v>0.2134314</v>
       </c>
       <c r="N92">
-        <v>0.137914</v>
+        <v>0.1355686</v>
       </c>
       <c r="O92">
-        <v>0.01241226</v>
+        <v>0.012201174</v>
       </c>
       <c r="P92">
-        <v>0.12550174</v>
+        <v>0.123367426</v>
       </c>
       <c r="Q92">
-        <v>0.15950174</v>
+        <v>0.157367426</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6480028149257074</v>
+        <v>0.7142589582677935</v>
       </c>
       <c r="T92">
-        <v>8.762784718982369</v>
+        <v>9.726892335265038</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.653354556910454</v>
+        <v>1.635185825515833</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1388123062441014</v>
+        <v>0.1391143309956321</v>
       </c>
       <c r="C93">
-        <v>0.07107387807417975</v>
+        <v>0.04338422777418804</v>
       </c>
       <c r="D93">
-        <v>1.21253387807418</v>
+        <v>1.210904227774189</v>
       </c>
       <c r="E93">
-        <v>2.23546</v>
+        <v>2.26152</v>
       </c>
       <c r="F93">
-        <v>2.37146</v>
+        <v>2.397520000000001</v>
       </c>
       <c r="G93">
         <v>1.23</v>
@@ -8895,28 +8895,28 @@
         <v>0.349</v>
       </c>
       <c r="M93">
-        <v>0.2134314</v>
+        <v>0.2157768</v>
       </c>
       <c r="N93">
-        <v>0.1355686</v>
+        <v>0.1332231999999999</v>
       </c>
       <c r="O93">
-        <v>0.012201174</v>
+        <v>0.01199008799999999</v>
       </c>
       <c r="P93">
-        <v>0.123367426</v>
+        <v>0.1212331119999999</v>
       </c>
       <c r="Q93">
-        <v>0.157367426</v>
+        <v>0.155233112</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7142589582677935</v>
+        <v>0.7970791374454014</v>
       </c>
       <c r="T93">
-        <v>9.726892335265038</v>
+        <v>10.93202685561838</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.635185825515833</v>
+        <v>1.617412066542835</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1391143309956321</v>
+        <v>0.1394163557471627</v>
       </c>
       <c r="C94">
-        <v>0.04338422777418804</v>
+        <v>0.0156989521074955</v>
       </c>
       <c r="D94">
-        <v>1.210904227774189</v>
+        <v>1.209278952107496</v>
       </c>
       <c r="E94">
-        <v>2.26152</v>
+        <v>2.28758</v>
       </c>
       <c r="F94">
-        <v>2.397520000000001</v>
+        <v>2.42358</v>
       </c>
       <c r="G94">
         <v>1.23</v>
@@ -8977,28 +8977,28 @@
         <v>0.349</v>
       </c>
       <c r="M94">
-        <v>0.2157768</v>
+        <v>0.2181222</v>
       </c>
       <c r="N94">
-        <v>0.1332231999999999</v>
+        <v>0.1308778</v>
       </c>
       <c r="O94">
-        <v>0.01199008799999999</v>
+        <v>0.011779002</v>
       </c>
       <c r="P94">
-        <v>0.1212331119999999</v>
+        <v>0.119098798</v>
       </c>
       <c r="Q94">
-        <v>0.155233112</v>
+        <v>0.153098798</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7970791374454014</v>
+        <v>0.9035622249594684</v>
       </c>
       <c r="T94">
-        <v>10.93202685561838</v>
+        <v>12.4814855246441</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.617412066542835</v>
+        <v>1.6000205389456</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1394163557471627</v>
+        <v>0.1397183804986934</v>
       </c>
       <c r="C95">
-        <v>0.0156989521074955</v>
+        <v>-0.01198196651718764</v>
       </c>
       <c r="D95">
-        <v>1.209278952107496</v>
+        <v>1.207658033482813</v>
       </c>
       <c r="E95">
-        <v>2.28758</v>
+        <v>2.31364</v>
       </c>
       <c r="F95">
-        <v>2.42358</v>
+        <v>2.44964</v>
       </c>
       <c r="G95">
         <v>1.23</v>
@@ -9059,28 +9059,28 @@
         <v>0.349</v>
       </c>
       <c r="M95">
-        <v>0.2181222</v>
+        <v>0.2204676</v>
       </c>
       <c r="N95">
-        <v>0.1308778</v>
+        <v>0.1285323999999999</v>
       </c>
       <c r="O95">
-        <v>0.011779002</v>
+        <v>0.01156791599999999</v>
       </c>
       <c r="P95">
-        <v>0.119098798</v>
+        <v>0.1169644839999999</v>
       </c>
       <c r="Q95">
-        <v>0.153098798</v>
+        <v>0.150964484</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9035622249594684</v>
+        <v>1.045539674978225</v>
       </c>
       <c r="T95">
-        <v>12.4814855246441</v>
+        <v>14.5474304166784</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.6000205389456</v>
+        <v>1.582999043850434</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1397183804986934</v>
+        <v>0.1400204052502241</v>
       </c>
       <c r="C96">
-        <v>-0.01198196651718764</v>
+        <v>-0.03965854559695625</v>
       </c>
       <c r="D96">
-        <v>1.207658033482813</v>
+        <v>1.206041454403045</v>
       </c>
       <c r="E96">
-        <v>2.31364</v>
+        <v>2.339700000000001</v>
       </c>
       <c r="F96">
-        <v>2.44964</v>
+        <v>2.475700000000001</v>
       </c>
       <c r="G96">
         <v>1.23</v>
@@ -9141,28 +9141,28 @@
         <v>0.349</v>
       </c>
       <c r="M96">
-        <v>0.2204676</v>
+        <v>0.2228130000000001</v>
       </c>
       <c r="N96">
-        <v>0.1285323999999999</v>
+        <v>0.1261869999999999</v>
       </c>
       <c r="O96">
-        <v>0.01156791599999999</v>
+        <v>0.01135682999999999</v>
       </c>
       <c r="P96">
-        <v>0.1169644839999999</v>
+        <v>0.1148301699999999</v>
       </c>
       <c r="Q96">
-        <v>0.150964484</v>
+        <v>0.14883017</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.045539674978225</v>
+        <v>1.244308105004484</v>
       </c>
       <c r="T96">
-        <v>14.5474304166784</v>
+        <v>17.43975326552641</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.582999043850434</v>
+        <v>1.566335896020429</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1400204052502241</v>
+        <v>0.1403224300017548</v>
       </c>
       <c r="C97">
-        <v>-0.03965854559695625</v>
+        <v>-0.06733080253534451</v>
       </c>
       <c r="D97">
-        <v>1.206041454403045</v>
+        <v>1.204429197464656</v>
       </c>
       <c r="E97">
-        <v>2.339700000000001</v>
+        <v>2.36576</v>
       </c>
       <c r="F97">
-        <v>2.475700000000001</v>
+        <v>2.50176</v>
       </c>
       <c r="G97">
         <v>1.23</v>
@@ -9223,28 +9223,28 @@
         <v>0.349</v>
       </c>
       <c r="M97">
-        <v>0.2228130000000001</v>
+        <v>0.2251584</v>
       </c>
       <c r="N97">
-        <v>0.1261869999999999</v>
+        <v>0.1238415999999999</v>
       </c>
       <c r="O97">
-        <v>0.01135682999999999</v>
+        <v>0.01114574399999999</v>
       </c>
       <c r="P97">
-        <v>0.1148301699999999</v>
+        <v>0.1126958559999999</v>
       </c>
       <c r="Q97">
-        <v>0.14883017</v>
+        <v>0.146695856</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.244308105004484</v>
+        <v>1.542460750043872</v>
       </c>
       <c r="T97">
-        <v>17.43975326552641</v>
+        <v>21.77823753879844</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.566335896020429</v>
+        <v>1.55001989710355</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1403224300017548</v>
+        <v>0.1406244547532854</v>
       </c>
       <c r="C98">
-        <v>-0.06733080253534451</v>
+        <v>-0.09499875464295116</v>
       </c>
       <c r="D98">
-        <v>1.204429197464656</v>
+        <v>1.202821245357049</v>
       </c>
       <c r="E98">
-        <v>2.36576</v>
+        <v>2.39182</v>
       </c>
       <c r="F98">
-        <v>2.50176</v>
+        <v>2.52782</v>
       </c>
       <c r="G98">
         <v>1.23</v>
@@ -9305,28 +9305,28 @@
         <v>0.349</v>
       </c>
       <c r="M98">
-        <v>0.2251584</v>
+        <v>0.2275038</v>
       </c>
       <c r="N98">
-        <v>0.1238415999999999</v>
+        <v>0.1214962</v>
       </c>
       <c r="O98">
-        <v>0.01114574399999999</v>
+        <v>0.010934658</v>
       </c>
       <c r="P98">
-        <v>0.1126958559999999</v>
+        <v>0.110561542</v>
       </c>
       <c r="Q98">
-        <v>0.146695856</v>
+        <v>0.144561542</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.542460750043868</v>
+        <v>2.039381825109513</v>
       </c>
       <c r="T98">
-        <v>21.77823753879838</v>
+        <v>29.00904466091839</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.55001989710355</v>
+        <v>1.534040310535472</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1406244547532854</v>
+        <v>0.1409264795048161</v>
       </c>
       <c r="C99">
-        <v>-0.09499875464295116</v>
+        <v>-0.1226624191380559</v>
       </c>
       <c r="D99">
-        <v>1.202821245357049</v>
+        <v>1.201217580861945</v>
       </c>
       <c r="E99">
-        <v>2.39182</v>
+        <v>2.41788</v>
       </c>
       <c r="F99">
-        <v>2.52782</v>
+        <v>2.55388</v>
       </c>
       <c r="G99">
         <v>1.23</v>
@@ -9387,28 +9387,28 @@
         <v>0.349</v>
       </c>
       <c r="M99">
-        <v>0.2275038</v>
+        <v>0.2298492</v>
       </c>
       <c r="N99">
-        <v>0.1214962</v>
+        <v>0.1191507999999999</v>
       </c>
       <c r="O99">
-        <v>0.010934658</v>
+        <v>0.010723572</v>
       </c>
       <c r="P99">
-        <v>0.110561542</v>
+        <v>0.1084272279999999</v>
       </c>
       <c r="Q99">
-        <v>0.144561542</v>
+        <v>0.142427228</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.039381825109513</v>
+        <v>3.033223975240802</v>
       </c>
       <c r="T99">
-        <v>29.00904466091839</v>
+        <v>43.47065890515841</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.534040310535472</v>
+        <v>1.518386837978988</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1409264795048161</v>
+        <v>0.1412285042563468</v>
       </c>
       <c r="C100">
-        <v>-0.1226624191380559</v>
+        <v>-0.1503218131472344</v>
       </c>
       <c r="D100">
-        <v>1.201217580861945</v>
+        <v>1.199618186852766</v>
       </c>
       <c r="E100">
-        <v>2.41788</v>
+        <v>2.44394</v>
       </c>
       <c r="F100">
-        <v>2.55388</v>
+        <v>2.57994</v>
       </c>
       <c r="G100">
         <v>1.23</v>
@@ -9469,28 +9469,28 @@
         <v>0.349</v>
       </c>
       <c r="M100">
-        <v>0.2298492</v>
+        <v>0.2321946</v>
       </c>
       <c r="N100">
-        <v>0.1191507999999999</v>
+        <v>0.1168054</v>
       </c>
       <c r="O100">
-        <v>0.010723572</v>
+        <v>0.010512486</v>
       </c>
       <c r="P100">
-        <v>0.1084272279999999</v>
+        <v>0.106292914</v>
       </c>
       <c r="Q100">
-        <v>0.142427228</v>
+        <v>0.140292914</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.033223975240802</v>
+        <v>6.014750425634673</v>
       </c>
       <c r="T100">
-        <v>43.47065890515841</v>
+        <v>86.85550163787848</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.518386837978988</v>
+        <v>1.503049597191321</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1412285042563468</v>
-      </c>
-      <c r="C101">
-        <v>-0.1503218131472344</v>
-      </c>
-      <c r="D101">
-        <v>1.199618186852766</v>
-      </c>
-      <c r="E101">
-        <v>2.44394</v>
-      </c>
-      <c r="F101">
-        <v>2.57994</v>
-      </c>
-      <c r="G101">
-        <v>1.23</v>
-      </c>
-      <c r="H101">
-        <v>2.47</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.383</v>
-      </c>
-      <c r="K101">
-        <v>0.03400000000000003</v>
-      </c>
-      <c r="L101">
-        <v>0.349</v>
-      </c>
-      <c r="M101">
-        <v>0.2321946</v>
-      </c>
-      <c r="N101">
-        <v>0.1168054</v>
-      </c>
-      <c r="O101">
-        <v>0.010512486</v>
-      </c>
-      <c r="P101">
-        <v>0.106292914</v>
-      </c>
-      <c r="Q101">
-        <v>0.140292914</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.014750425634673</v>
-      </c>
-      <c r="T101">
-        <v>86.85550163787848</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.0819</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.503049597191321</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
